--- a/data/nzd0299/nzd0299.xlsx
+++ b/data/nzd0299/nzd0299.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X299"/>
+  <dimension ref="A1:X300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23724,6 +23724,84 @@
         <v>361.31</v>
       </c>
       <c r="X299" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:07:08+00:00</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>360.94</v>
+      </c>
+      <c r="C300" t="n">
+        <v>358.18</v>
+      </c>
+      <c r="D300" t="n">
+        <v>348.28</v>
+      </c>
+      <c r="E300" t="n">
+        <v>346.69</v>
+      </c>
+      <c r="F300" t="n">
+        <v>337.81</v>
+      </c>
+      <c r="G300" t="n">
+        <v>333.85</v>
+      </c>
+      <c r="H300" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="I300" t="n">
+        <v>332.14</v>
+      </c>
+      <c r="J300" t="n">
+        <v>327</v>
+      </c>
+      <c r="K300" t="n">
+        <v>329.84</v>
+      </c>
+      <c r="L300" t="n">
+        <v>331.21</v>
+      </c>
+      <c r="M300" t="n">
+        <v>334.15</v>
+      </c>
+      <c r="N300" t="n">
+        <v>337.29</v>
+      </c>
+      <c r="O300" t="n">
+        <v>355.13</v>
+      </c>
+      <c r="P300" t="n">
+        <v>352.23</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>357.86</v>
+      </c>
+      <c r="R300" t="n">
+        <v>362.35</v>
+      </c>
+      <c r="S300" t="n">
+        <v>355.71</v>
+      </c>
+      <c r="T300" t="n">
+        <v>339.24</v>
+      </c>
+      <c r="U300" t="n">
+        <v>348.9</v>
+      </c>
+      <c r="V300" t="n">
+        <v>356.93</v>
+      </c>
+      <c r="W300" t="n">
+        <v>366.33</v>
+      </c>
+      <c r="X300" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23740,7 +23818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B305"/>
+  <dimension ref="A1:B306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26793,6 +26871,16 @@
       </c>
       <c r="B305" t="n">
         <v>1.1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -26961,28 +27049,28 @@
         <v>0.0497</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5180106068312341</v>
+        <v>-0.5080324539813038</v>
       </c>
       <c r="J2" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K2" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07684699267448492</v>
+        <v>0.07426265061967241</v>
       </c>
       <c r="M2" t="n">
-        <v>9.194318335698112</v>
+        <v>9.199794781106963</v>
       </c>
       <c r="N2" t="n">
-        <v>175.0938035572829</v>
+        <v>175.3289310901291</v>
       </c>
       <c r="O2" t="n">
-        <v>13.23230152155259</v>
+        <v>13.24118314540393</v>
       </c>
       <c r="P2" t="n">
-        <v>358.5750348295352</v>
+        <v>358.4730639353793</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27039,28 +27127,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3286087748094323</v>
+        <v>-0.3195402055688828</v>
       </c>
       <c r="J3" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K3" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06295836692171053</v>
+        <v>0.059675048127104</v>
       </c>
       <c r="M3" t="n">
-        <v>7.52984355170487</v>
+        <v>7.551362103047946</v>
       </c>
       <c r="N3" t="n">
-        <v>85.80054113065448</v>
+        <v>86.17400527953585</v>
       </c>
       <c r="O3" t="n">
-        <v>9.262858151275688</v>
+        <v>9.282995490655797</v>
       </c>
       <c r="P3" t="n">
-        <v>352.5698203327481</v>
+        <v>352.4759067670977</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27117,28 +27205,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2433562050270576</v>
+        <v>-0.2373952604786415</v>
       </c>
       <c r="J4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K4" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01834792876854474</v>
+        <v>0.01755958975342609</v>
       </c>
       <c r="M4" t="n">
-        <v>9.527866041059079</v>
+        <v>9.525077297748425</v>
       </c>
       <c r="N4" t="n">
-        <v>170.5323827956232</v>
+        <v>170.2465690090023</v>
       </c>
       <c r="O4" t="n">
-        <v>13.05880479966001</v>
+        <v>13.04785687417678</v>
       </c>
       <c r="P4" t="n">
-        <v>345.2494601279155</v>
+        <v>345.1879589637224</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27195,28 +27283,28 @@
         <v>0.0751</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4847399502107691</v>
+        <v>-0.4757780026637018</v>
       </c>
       <c r="J5" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K5" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07023413614661522</v>
+        <v>0.06800157385763406</v>
       </c>
       <c r="M5" t="n">
-        <v>8.730603254620764</v>
+        <v>8.747065354095861</v>
       </c>
       <c r="N5" t="n">
-        <v>170.3773078948778</v>
+        <v>170.4721437898698</v>
       </c>
       <c r="O5" t="n">
-        <v>13.05286588818248</v>
+        <v>13.05649814421424</v>
       </c>
       <c r="P5" t="n">
-        <v>345.0530878900288</v>
+        <v>344.9617590951975</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27273,28 +27361,28 @@
         <v>0.0921</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1711884308017035</v>
+        <v>-0.1675506490789296</v>
       </c>
       <c r="J6" t="n">
+        <v>299</v>
+      </c>
+      <c r="K6" t="n">
         <v>298</v>
       </c>
-      <c r="K6" t="n">
-        <v>297</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0137554672125445</v>
+        <v>0.01325802514678365</v>
       </c>
       <c r="M6" t="n">
-        <v>8.388252794950558</v>
+        <v>8.378494683664192</v>
       </c>
       <c r="N6" t="n">
-        <v>114.4666058366533</v>
+        <v>114.1920358736482</v>
       </c>
       <c r="O6" t="n">
-        <v>10.69890675894754</v>
+        <v>10.68606737175319</v>
       </c>
       <c r="P6" t="n">
-        <v>336.485779972472</v>
+        <v>336.4486441604716</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27351,28 +27439,28 @@
         <v>0.0756</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2515106010105849</v>
+        <v>-0.2501817010215271</v>
       </c>
       <c r="J7" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K7" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01827831297350591</v>
+        <v>0.01820585243768524</v>
       </c>
       <c r="M7" t="n">
-        <v>10.55673717357424</v>
+        <v>10.52698473883678</v>
       </c>
       <c r="N7" t="n">
-        <v>181.380730804504</v>
+        <v>180.7842444882185</v>
       </c>
       <c r="O7" t="n">
-        <v>13.46776636285706</v>
+        <v>13.44560316565302</v>
       </c>
       <c r="P7" t="n">
-        <v>338.2767490219826</v>
+        <v>338.2629870124468</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27429,28 +27517,28 @@
         <v>0.076</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2781542532218624</v>
+        <v>-0.2784192655677344</v>
       </c>
       <c r="J8" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K8" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02212910967747084</v>
+        <v>0.02231358738359202</v>
       </c>
       <c r="M8" t="n">
-        <v>10.26109591591067</v>
+        <v>10.22839815785673</v>
       </c>
       <c r="N8" t="n">
-        <v>185.7101525053123</v>
+        <v>185.0896272513973</v>
       </c>
       <c r="O8" t="n">
-        <v>13.62755122923089</v>
+        <v>13.60476487306551</v>
       </c>
       <c r="P8" t="n">
-        <v>338.1024470616347</v>
+        <v>338.1051553330229</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27507,28 +27595,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3933055289436179</v>
+        <v>-0.3913312847268384</v>
       </c>
       <c r="J9" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0396618791069564</v>
+        <v>0.03952377503823423</v>
       </c>
       <c r="M9" t="n">
-        <v>10.86928997201907</v>
+        <v>10.84137884347957</v>
       </c>
       <c r="N9" t="n">
-        <v>202.7410870397543</v>
+        <v>202.0904642398253</v>
       </c>
       <c r="O9" t="n">
-        <v>14.23871788609334</v>
+        <v>14.21585256816577</v>
       </c>
       <c r="P9" t="n">
-        <v>339.2007492889971</v>
+        <v>339.1804877351191</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27585,28 +27673,28 @@
         <v>0.0916</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.172239984904709</v>
+        <v>-0.1747661454760866</v>
       </c>
       <c r="J10" t="n">
+        <v>299</v>
+      </c>
+      <c r="K10" t="n">
         <v>298</v>
       </c>
-      <c r="K10" t="n">
-        <v>297</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.008338533998143882</v>
+        <v>0.008636792867458998</v>
       </c>
       <c r="M10" t="n">
-        <v>10.85258890238985</v>
+        <v>10.83107629225205</v>
       </c>
       <c r="N10" t="n">
-        <v>190.4151045845408</v>
+        <v>189.8283113106395</v>
       </c>
       <c r="O10" t="n">
-        <v>13.79909796271266</v>
+        <v>13.77781954122783</v>
       </c>
       <c r="P10" t="n">
-        <v>335.4059514950598</v>
+        <v>335.4319048692889</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27663,28 +27751,28 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1383611129868268</v>
+        <v>-0.1379677887670903</v>
       </c>
       <c r="J11" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K11" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L11" t="n">
-        <v>0.006092796667536593</v>
+        <v>0.006098176203212624</v>
       </c>
       <c r="M11" t="n">
-        <v>10.57456058559302</v>
+        <v>10.54099923916777</v>
       </c>
       <c r="N11" t="n">
-        <v>169.6304861485258</v>
+        <v>169.0644353687304</v>
       </c>
       <c r="O11" t="n">
-        <v>13.02422689254628</v>
+        <v>13.00247804723124</v>
       </c>
       <c r="P11" t="n">
-        <v>332.796131859058</v>
+        <v>332.7921123152624</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27741,28 +27829,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.02274014729399099</v>
+        <v>-0.02143590327814649</v>
       </c>
       <c r="J12" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K12" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L12" t="n">
-        <v>0.000155977197994428</v>
+        <v>0.0001395060243184476</v>
       </c>
       <c r="M12" t="n">
-        <v>11.15108364722824</v>
+        <v>11.1193875539428</v>
       </c>
       <c r="N12" t="n">
-        <v>180.0546521354351</v>
+        <v>179.4664848372866</v>
       </c>
       <c r="O12" t="n">
-        <v>13.41844447525253</v>
+        <v>13.39651017382089</v>
       </c>
       <c r="P12" t="n">
-        <v>329.7356858591453</v>
+        <v>329.7223572470771</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27819,28 +27907,28 @@
         <v>0.0853</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.04905901462426565</v>
+        <v>-0.04650775456439021</v>
       </c>
       <c r="J13" t="n">
+        <v>299</v>
+      </c>
+      <c r="K13" t="n">
         <v>298</v>
       </c>
-      <c r="K13" t="n">
-        <v>297</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.0006813765034948682</v>
+        <v>0.0006162783616285861</v>
       </c>
       <c r="M13" t="n">
-        <v>11.17927315521713</v>
+        <v>11.15065060506979</v>
       </c>
       <c r="N13" t="n">
-        <v>190.0951191505365</v>
+        <v>189.5102570211999</v>
       </c>
       <c r="O13" t="n">
-        <v>13.78749865459781</v>
+        <v>13.7662724446816</v>
       </c>
       <c r="P13" t="n">
-        <v>331.417551578694</v>
+        <v>331.3913058117562</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27897,28 +27985,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2721660200531484</v>
+        <v>-0.2683773512409506</v>
       </c>
       <c r="J14" t="n">
+        <v>299</v>
+      </c>
+      <c r="K14" t="n">
         <v>298</v>
       </c>
-      <c r="K14" t="n">
-        <v>297</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.01780229285606039</v>
+        <v>0.01742233072108013</v>
       </c>
       <c r="M14" t="n">
-        <v>11.5583997935569</v>
+        <v>11.53345577501961</v>
       </c>
       <c r="N14" t="n">
-        <v>220.0935302760625</v>
+        <v>219.4719315632377</v>
       </c>
       <c r="O14" t="n">
-        <v>14.83554954412079</v>
+        <v>14.81458509588567</v>
       </c>
       <c r="P14" t="n">
-        <v>338.3810092029379</v>
+        <v>338.3420337491169</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27975,28 +28063,28 @@
         <v>0.0414</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1293366599671909</v>
+        <v>-0.1172727196330124</v>
       </c>
       <c r="J15" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K15" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003821668006295798</v>
+        <v>0.00314902846331977</v>
       </c>
       <c r="M15" t="n">
-        <v>9.601575728016899</v>
+        <v>9.613475893245303</v>
       </c>
       <c r="N15" t="n">
-        <v>233.5643887513227</v>
+        <v>233.9564059546018</v>
       </c>
       <c r="O15" t="n">
-        <v>15.28281350901472</v>
+        <v>15.29563355845719</v>
       </c>
       <c r="P15" t="n">
-        <v>339.6661419317494</v>
+        <v>339.5414599764325</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28053,28 +28141,28 @@
         <v>0.0699</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.86159199361659</v>
+        <v>-0.8422274566054924</v>
       </c>
       <c r="J16" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K16" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07481742775245981</v>
+        <v>0.07175825111151501</v>
       </c>
       <c r="M16" t="n">
-        <v>17.41880814618204</v>
+        <v>17.4193685704472</v>
       </c>
       <c r="N16" t="n">
-        <v>490.2528417374452</v>
+        <v>491.623843005419</v>
       </c>
       <c r="O16" t="n">
-        <v>22.14165399732923</v>
+        <v>22.17259215800938</v>
       </c>
       <c r="P16" t="n">
-        <v>344.4198320026433</v>
+        <v>344.2188335526641</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28131,28 +28219,28 @@
         <v>0.074</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1774883671118668</v>
+        <v>-0.1588186948846163</v>
       </c>
       <c r="J17" t="n">
+        <v>299</v>
+      </c>
+      <c r="K17" t="n">
         <v>298</v>
       </c>
-      <c r="K17" t="n">
-        <v>297</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.00296370239096666</v>
+        <v>0.002378207361916407</v>
       </c>
       <c r="M17" t="n">
-        <v>18.13089009675802</v>
+        <v>18.11522843031026</v>
       </c>
       <c r="N17" t="n">
-        <v>572.6586149803853</v>
+        <v>573.5925583128962</v>
       </c>
       <c r="O17" t="n">
-        <v>23.93028656285556</v>
+        <v>23.94979244822168</v>
       </c>
       <c r="P17" t="n">
-        <v>333.1263158083074</v>
+        <v>332.9346479342926</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28209,28 +28297,28 @@
         <v>0.0771</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4782855668344373</v>
+        <v>-0.4522923246682784</v>
       </c>
       <c r="J18" t="n">
+        <v>299</v>
+      </c>
+      <c r="K18" t="n">
         <v>298</v>
       </c>
-      <c r="K18" t="n">
-        <v>297</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.01627076649309245</v>
+        <v>0.01456375936172549</v>
       </c>
       <c r="M18" t="n">
-        <v>21.66743406655297</v>
+        <v>21.6786195063114</v>
       </c>
       <c r="N18" t="n">
-        <v>747.3460575471735</v>
+        <v>750.3735644527796</v>
       </c>
       <c r="O18" t="n">
-        <v>27.33763079616033</v>
+        <v>27.39294734877537</v>
       </c>
       <c r="P18" t="n">
-        <v>333.8837023313674</v>
+        <v>333.6168487195791</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28287,28 +28375,28 @@
         <v>0.1693</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6264891321424014</v>
+        <v>-0.604393677877607</v>
       </c>
       <c r="J19" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K19" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02960235723315396</v>
+        <v>0.02763126684577655</v>
       </c>
       <c r="M19" t="n">
-        <v>20.98741987543144</v>
+        <v>20.98324016250618</v>
       </c>
       <c r="N19" t="n">
-        <v>689.1753424002718</v>
+        <v>690.8079251230573</v>
       </c>
       <c r="O19" t="n">
-        <v>26.25214929106323</v>
+        <v>26.28322516593154</v>
       </c>
       <c r="P19" t="n">
-        <v>337.4500987275988</v>
+        <v>337.221740134549</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28365,28 +28453,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9096328769781191</v>
+        <v>-0.8978192381057899</v>
       </c>
       <c r="J20" t="n">
+        <v>299</v>
+      </c>
+      <c r="K20" t="n">
         <v>298</v>
       </c>
-      <c r="K20" t="n">
-        <v>297</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.08992343198397268</v>
+        <v>0.08813262034375102</v>
       </c>
       <c r="M20" t="n">
-        <v>15.64438744742313</v>
+        <v>15.63114584788552</v>
       </c>
       <c r="N20" t="n">
-        <v>452.4983379043901</v>
+        <v>452.1232757734584</v>
       </c>
       <c r="O20" t="n">
-        <v>21.27200831854835</v>
+        <v>21.26319063013494</v>
       </c>
       <c r="P20" t="n">
-        <v>344.1774025523911</v>
+        <v>344.0561205598912</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28443,28 +28531,28 @@
         <v>0.1793</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4592006969108324</v>
+        <v>-0.4460502602703313</v>
       </c>
       <c r="J21" t="n">
+        <v>299</v>
+      </c>
+      <c r="K21" t="n">
         <v>298</v>
       </c>
-      <c r="K21" t="n">
-        <v>297</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.04886261804882042</v>
+        <v>0.04624069490769567</v>
       </c>
       <c r="M21" t="n">
-        <v>11.21048928912629</v>
+        <v>11.22482630101694</v>
       </c>
       <c r="N21" t="n">
-        <v>221.7947321792831</v>
+        <v>222.4672490078395</v>
       </c>
       <c r="O21" t="n">
-        <v>14.89277449568357</v>
+        <v>14.91533603402349</v>
       </c>
       <c r="P21" t="n">
-        <v>340.1096262509447</v>
+        <v>339.9746203331882</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28521,28 +28609,28 @@
         <v>0.1333</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8825169906135024</v>
+        <v>-0.8605062654727469</v>
       </c>
       <c r="J22" t="n">
+        <v>299</v>
+      </c>
+      <c r="K22" t="n">
         <v>298</v>
       </c>
-      <c r="K22" t="n">
-        <v>297</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.06735158714380629</v>
+        <v>0.06423407857733532</v>
       </c>
       <c r="M22" t="n">
-        <v>19.43930555930343</v>
+        <v>19.44155344942517</v>
       </c>
       <c r="N22" t="n">
-        <v>582.7682781934702</v>
+        <v>584.7818088411479</v>
       </c>
       <c r="O22" t="n">
-        <v>24.14059399007138</v>
+        <v>24.18226227715571</v>
       </c>
       <c r="P22" t="n">
-        <v>345.1540932553384</v>
+        <v>344.9281252339449</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28599,28 +28687,28 @@
         <v>0.0785</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.238369411360416</v>
+        <v>-1.210604512615825</v>
       </c>
       <c r="J23" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K23" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1256456446317659</v>
+        <v>0.1202933999719533</v>
       </c>
       <c r="M23" t="n">
-        <v>19.89282782225469</v>
+        <v>19.9412845709807</v>
       </c>
       <c r="N23" t="n">
-        <v>569.1786648472814</v>
+        <v>573.4580460875196</v>
       </c>
       <c r="O23" t="n">
-        <v>23.85746559983439</v>
+        <v>23.94698407080774</v>
       </c>
       <c r="P23" t="n">
-        <v>355.343060033322</v>
+        <v>355.054469768695</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28658,7 +28746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X299"/>
+  <dimension ref="A1:X300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65003,6 +65091,128 @@
         </is>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:07:08+00:00</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>-39.86393088780184,174.8182213276767</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>-39.86367401553,174.81738654564413</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>-39.86335634708858,174.81657898355866</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>-39.86310943577917,174.81573974213202</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>-39.86280045127182,174.81492829314246</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>-39.86253335869311,174.8140980879623</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>-39.86227145941796,174.81326555761248</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>-39.862052047775094,174.81241400304555</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>-39.861774905772954,174.81158829773696</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>-39.8615657101406,174.81073216799535</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>-39.86134399709422,174.80988164261623</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>-39.86113565117784,174.80902513100975</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>-39.86092900729529,174.8081678564845</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>-39.860847527071385,174.80725453179966</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>-39.86058945310288,174.80642028599954</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>-39.860404007653635,174.80555351536407</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>-39.86020885464466,174.8046910909771</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>-39.859918933976964,174.80387110647268</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>-39.85954531503008,174.80308860644266</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>-39.85939417969569,174.80220646788473</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>-39.85922916464135,174.80133054384058</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>-39.859075813346784,174.80044939445486</t>
+        </is>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0299/nzd0299.xlsx
+++ b/data/nzd0299/nzd0299.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X300"/>
+  <dimension ref="A1:X301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23754,7 +23754,7 @@
         <v>333.85</v>
       </c>
       <c r="H300" t="n">
-        <v>330.5</v>
+        <v>330.29</v>
       </c>
       <c r="I300" t="n">
         <v>332.14</v>
@@ -23802,6 +23802,84 @@
         <v>366.33</v>
       </c>
       <c r="X300" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:06+00:00</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>359.36</v>
+      </c>
+      <c r="C301" t="n">
+        <v>356.87</v>
+      </c>
+      <c r="D301" t="n">
+        <v>347.27</v>
+      </c>
+      <c r="E301" t="n">
+        <v>345.8</v>
+      </c>
+      <c r="F301" t="n">
+        <v>337.38</v>
+      </c>
+      <c r="G301" t="n">
+        <v>333.49</v>
+      </c>
+      <c r="H301" t="n">
+        <v>330</v>
+      </c>
+      <c r="I301" t="n">
+        <v>331.36</v>
+      </c>
+      <c r="J301" t="n">
+        <v>328.04</v>
+      </c>
+      <c r="K301" t="n">
+        <v>331.11</v>
+      </c>
+      <c r="L301" t="n">
+        <v>334.1</v>
+      </c>
+      <c r="M301" t="n">
+        <v>337.1</v>
+      </c>
+      <c r="N301" t="n">
+        <v>340.57</v>
+      </c>
+      <c r="O301" t="n">
+        <v>358.04</v>
+      </c>
+      <c r="P301" t="n">
+        <v>355.11</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>359.77</v>
+      </c>
+      <c r="R301" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="S301" t="n">
+        <v>356.28</v>
+      </c>
+      <c r="T301" t="n">
+        <v>341.75</v>
+      </c>
+      <c r="U301" t="n">
+        <v>349.06</v>
+      </c>
+      <c r="V301" t="n">
+        <v>356.36</v>
+      </c>
+      <c r="W301" t="n">
+        <v>362.18</v>
+      </c>
+      <c r="X301" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23818,7 +23896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B306"/>
+  <dimension ref="A1:B307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26881,6 +26959,16 @@
       </c>
       <c r="B306" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -27049,28 +27137,28 @@
         <v>0.0497</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5080324539813038</v>
+        <v>-0.4991914148037344</v>
       </c>
       <c r="J2" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K2" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07426265061967241</v>
+        <v>0.07207481904875457</v>
       </c>
       <c r="M2" t="n">
-        <v>9.199794781106963</v>
+        <v>9.200975568221615</v>
       </c>
       <c r="N2" t="n">
-        <v>175.3289310901291</v>
+        <v>175.3940207206007</v>
       </c>
       <c r="O2" t="n">
-        <v>13.24118314540393</v>
+        <v>13.24364076531075</v>
       </c>
       <c r="P2" t="n">
-        <v>358.4730639353793</v>
+        <v>358.3825166251711</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27127,28 +27215,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3195402055688828</v>
+        <v>-0.311443433205178</v>
       </c>
       <c r="J3" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K3" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L3" t="n">
-        <v>0.059675048127104</v>
+        <v>0.05688136028324986</v>
       </c>
       <c r="M3" t="n">
-        <v>7.551362103047946</v>
+        <v>7.568021971891033</v>
       </c>
       <c r="N3" t="n">
-        <v>86.17400527953585</v>
+        <v>86.41710449183155</v>
       </c>
       <c r="O3" t="n">
-        <v>9.282995490655797</v>
+        <v>9.296080060532587</v>
       </c>
       <c r="P3" t="n">
-        <v>352.4759067670977</v>
+        <v>352.3918764603143</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27205,28 +27293,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2373952604786415</v>
+        <v>-0.232163620518471</v>
       </c>
       <c r="J4" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K4" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01755958975342609</v>
+        <v>0.01689364414703309</v>
       </c>
       <c r="M4" t="n">
-        <v>9.525077297748425</v>
+        <v>9.518777693620573</v>
       </c>
       <c r="N4" t="n">
-        <v>170.2465690090023</v>
+        <v>169.8987569691382</v>
       </c>
       <c r="O4" t="n">
-        <v>13.04785687417678</v>
+        <v>13.03452173917932</v>
       </c>
       <c r="P4" t="n">
-        <v>345.1879589637224</v>
+        <v>345.1338644666808</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27283,28 +27371,28 @@
         <v>0.0751</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4757780026637018</v>
+        <v>-0.4675052558851789</v>
       </c>
       <c r="J5" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K5" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06800157385763406</v>
+        <v>0.06600528194737765</v>
       </c>
       <c r="M5" t="n">
-        <v>8.747065354095861</v>
+        <v>8.7604004559853</v>
       </c>
       <c r="N5" t="n">
-        <v>170.4721437898698</v>
+        <v>170.4740254414848</v>
       </c>
       <c r="O5" t="n">
-        <v>13.05649814421424</v>
+        <v>13.05657020206627</v>
       </c>
       <c r="P5" t="n">
-        <v>344.9617590951975</v>
+        <v>344.8772667061452</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27361,28 +27449,28 @@
         <v>0.0921</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1675506490789296</v>
+        <v>-0.1642352263699711</v>
       </c>
       <c r="J6" t="n">
+        <v>300</v>
+      </c>
+      <c r="K6" t="n">
         <v>299</v>
       </c>
-      <c r="K6" t="n">
-        <v>298</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01325802514678365</v>
+        <v>0.01281761951122373</v>
       </c>
       <c r="M6" t="n">
-        <v>8.378494683664192</v>
+        <v>8.367100177998019</v>
       </c>
       <c r="N6" t="n">
-        <v>114.1920358736482</v>
+        <v>113.9018469085391</v>
       </c>
       <c r="O6" t="n">
-        <v>10.68606737175319</v>
+        <v>10.67248082258943</v>
       </c>
       <c r="P6" t="n">
-        <v>336.4486441604716</v>
+        <v>336.4147248681368</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27439,28 +27527,28 @@
         <v>0.0756</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2501817010215271</v>
+        <v>-0.2490937442413236</v>
       </c>
       <c r="J7" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K7" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01820585243768524</v>
+        <v>0.01816704610174824</v>
       </c>
       <c r="M7" t="n">
-        <v>10.52698473883678</v>
+        <v>10.49636269551665</v>
       </c>
       <c r="N7" t="n">
-        <v>180.7842444882185</v>
+        <v>180.187196194607</v>
       </c>
       <c r="O7" t="n">
-        <v>13.44560316565302</v>
+        <v>13.42338244238787</v>
       </c>
       <c r="P7" t="n">
-        <v>338.2629870124468</v>
+        <v>338.2516959278144</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27517,28 +27605,28 @@
         <v>0.076</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2784192655677344</v>
+        <v>-0.2791232871367745</v>
       </c>
       <c r="J8" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K8" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02231358738359202</v>
+        <v>0.02256783235224202</v>
       </c>
       <c r="M8" t="n">
-        <v>10.22839815785673</v>
+        <v>10.19858058628139</v>
       </c>
       <c r="N8" t="n">
-        <v>185.0896272513973</v>
+        <v>184.4760928718142</v>
       </c>
       <c r="O8" t="n">
-        <v>13.60476487306551</v>
+        <v>13.58219764514617</v>
       </c>
       <c r="P8" t="n">
-        <v>338.1051553330229</v>
+        <v>338.1123627270808</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27595,28 +27683,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3913312847268384</v>
+        <v>-0.3898703949402894</v>
       </c>
       <c r="J9" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03952377503823423</v>
+        <v>0.03948550830739783</v>
       </c>
       <c r="M9" t="n">
-        <v>10.84137884347957</v>
+        <v>10.81137087224888</v>
       </c>
       <c r="N9" t="n">
-        <v>202.0904642398253</v>
+        <v>201.4299752387081</v>
       </c>
       <c r="O9" t="n">
-        <v>14.21585256816577</v>
+        <v>14.19260283523456</v>
       </c>
       <c r="P9" t="n">
-        <v>339.1804877351191</v>
+        <v>339.1654619371913</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27673,28 +27761,28 @@
         <v>0.0916</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1747661454760866</v>
+        <v>-0.1765866487245554</v>
       </c>
       <c r="J10" t="n">
+        <v>300</v>
+      </c>
+      <c r="K10" t="n">
         <v>299</v>
       </c>
-      <c r="K10" t="n">
-        <v>298</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.008636792867458998</v>
+        <v>0.008872380668788815</v>
       </c>
       <c r="M10" t="n">
-        <v>10.83107629225205</v>
+        <v>10.80551893183642</v>
       </c>
       <c r="N10" t="n">
-        <v>189.8283113106395</v>
+        <v>189.2207540854439</v>
       </c>
       <c r="O10" t="n">
-        <v>13.77781954122783</v>
+        <v>13.7557534902834</v>
       </c>
       <c r="P10" t="n">
-        <v>335.4319048692889</v>
+        <v>335.4506490790168</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27751,28 +27839,28 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1379677887670903</v>
+        <v>-0.1367780185690439</v>
       </c>
       <c r="J11" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K11" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L11" t="n">
-        <v>0.006098176203212624</v>
+        <v>0.0060328607831166</v>
       </c>
       <c r="M11" t="n">
-        <v>10.54099923916777</v>
+        <v>10.51127628281006</v>
       </c>
       <c r="N11" t="n">
-        <v>169.0644353687304</v>
+        <v>168.5126500767631</v>
       </c>
       <c r="O11" t="n">
-        <v>13.00247804723124</v>
+        <v>12.98124223935302</v>
       </c>
       <c r="P11" t="n">
-        <v>332.7921123152624</v>
+        <v>332.7799270405413</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27829,28 +27917,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.02143590327814649</v>
+        <v>-0.01832753733947037</v>
       </c>
       <c r="J12" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K12" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0001395060243184476</v>
+        <v>0.0001026092808606993</v>
       </c>
       <c r="M12" t="n">
-        <v>11.1193875539428</v>
+        <v>11.09555052691373</v>
       </c>
       <c r="N12" t="n">
-        <v>179.4664848372866</v>
+        <v>178.9485510622879</v>
       </c>
       <c r="O12" t="n">
-        <v>13.39651017382089</v>
+        <v>13.37716528500294</v>
       </c>
       <c r="P12" t="n">
-        <v>329.7223572470771</v>
+        <v>329.6905222818387</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27907,28 +27995,28 @@
         <v>0.0853</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.04650775456439021</v>
+        <v>-0.04211802988837451</v>
       </c>
       <c r="J13" t="n">
+        <v>300</v>
+      </c>
+      <c r="K13" t="n">
         <v>299</v>
       </c>
-      <c r="K13" t="n">
-        <v>298</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.0006162783616285861</v>
+        <v>0.0005083952991394858</v>
       </c>
       <c r="M13" t="n">
-        <v>11.15065060506979</v>
+        <v>11.12851851617971</v>
       </c>
       <c r="N13" t="n">
-        <v>189.5102570211999</v>
+        <v>189.0347391858188</v>
       </c>
       <c r="O13" t="n">
-        <v>13.7662724446816</v>
+        <v>13.74899047878857</v>
       </c>
       <c r="P13" t="n">
-        <v>331.3913058117562</v>
+        <v>331.3460491879118</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27985,28 +28073,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2683773512409506</v>
+        <v>-0.2625523240601417</v>
       </c>
       <c r="J14" t="n">
+        <v>300</v>
+      </c>
+      <c r="K14" t="n">
         <v>299</v>
       </c>
-      <c r="K14" t="n">
-        <v>298</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.01742233072108013</v>
+        <v>0.01677397062594976</v>
       </c>
       <c r="M14" t="n">
-        <v>11.53345577501961</v>
+        <v>11.51616710338232</v>
       </c>
       <c r="N14" t="n">
-        <v>219.4719315632377</v>
+        <v>219.0166461166845</v>
       </c>
       <c r="O14" t="n">
-        <v>14.81458509588567</v>
+        <v>14.79921099642425</v>
       </c>
       <c r="P14" t="n">
-        <v>338.3420337491169</v>
+        <v>338.2819796264869</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28063,28 +28151,28 @@
         <v>0.0414</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1172727196330124</v>
+        <v>-0.1035351209394346</v>
       </c>
       <c r="J15" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K15" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00314902846331977</v>
+        <v>0.002456174114798482</v>
       </c>
       <c r="M15" t="n">
-        <v>9.613475893245303</v>
+        <v>9.632340601580983</v>
       </c>
       <c r="N15" t="n">
-        <v>233.9564059546018</v>
+        <v>234.7117259885568</v>
       </c>
       <c r="O15" t="n">
-        <v>15.29563355845719</v>
+        <v>15.32030436997114</v>
       </c>
       <c r="P15" t="n">
-        <v>339.5414599764325</v>
+        <v>339.3991735572584</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28141,28 +28229,28 @@
         <v>0.0699</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8422274566054924</v>
+        <v>-0.8212999330525105</v>
       </c>
       <c r="J16" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K16" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07175825111151501</v>
+        <v>0.06843364063090152</v>
       </c>
       <c r="M16" t="n">
-        <v>17.4193685704472</v>
+        <v>17.42439173624901</v>
       </c>
       <c r="N16" t="n">
-        <v>491.623843005419</v>
+        <v>493.5335645277928</v>
       </c>
       <c r="O16" t="n">
-        <v>22.17259215800938</v>
+        <v>22.21561533083864</v>
       </c>
       <c r="P16" t="n">
-        <v>344.2188335526641</v>
+        <v>344.0011399411138</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28219,28 +28307,28 @@
         <v>0.074</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1588186948846163</v>
+        <v>-0.1392245379716801</v>
       </c>
       <c r="J17" t="n">
+        <v>300</v>
+      </c>
+      <c r="K17" t="n">
         <v>299</v>
       </c>
-      <c r="K17" t="n">
-        <v>298</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.002378207361916407</v>
+        <v>0.001830479320154232</v>
       </c>
       <c r="M17" t="n">
-        <v>18.11522843031026</v>
+        <v>18.10161722885368</v>
       </c>
       <c r="N17" t="n">
-        <v>573.5925583128962</v>
+        <v>574.8449502110434</v>
       </c>
       <c r="O17" t="n">
-        <v>23.94979244822168</v>
+        <v>23.97592438699796</v>
       </c>
       <c r="P17" t="n">
-        <v>332.9346479342926</v>
+        <v>332.7330512665968</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28297,28 +28385,28 @@
         <v>0.0771</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4522923246682784</v>
+        <v>-0.4260910309272333</v>
       </c>
       <c r="J18" t="n">
+        <v>300</v>
+      </c>
+      <c r="K18" t="n">
         <v>299</v>
       </c>
-      <c r="K18" t="n">
-        <v>298</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.01456375936172549</v>
+        <v>0.01293385806198177</v>
       </c>
       <c r="M18" t="n">
-        <v>21.6786195063114</v>
+        <v>21.69407787395277</v>
       </c>
       <c r="N18" t="n">
-        <v>750.3735644527796</v>
+        <v>753.5335993909932</v>
       </c>
       <c r="O18" t="n">
-        <v>27.39294734877537</v>
+        <v>27.45056646757937</v>
       </c>
       <c r="P18" t="n">
-        <v>333.6168487195791</v>
+        <v>333.347273788084</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28375,28 +28463,28 @@
         <v>0.1693</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.604393677877607</v>
+        <v>-0.5822608575793635</v>
       </c>
       <c r="J19" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K19" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02763126684577655</v>
+        <v>0.02571551160779517</v>
       </c>
       <c r="M19" t="n">
-        <v>20.98324016250618</v>
+        <v>20.98083264931789</v>
       </c>
       <c r="N19" t="n">
-        <v>690.8079251230573</v>
+        <v>692.4881922068421</v>
       </c>
       <c r="O19" t="n">
-        <v>26.28322516593154</v>
+        <v>26.31517038148988</v>
       </c>
       <c r="P19" t="n">
-        <v>337.221740134549</v>
+        <v>336.9925006716192</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28453,28 +28541,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8978192381057899</v>
+        <v>-0.884571135744325</v>
       </c>
       <c r="J20" t="n">
+        <v>300</v>
+      </c>
+      <c r="K20" t="n">
         <v>299</v>
       </c>
-      <c r="K20" t="n">
-        <v>298</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.08813262034375102</v>
+        <v>0.08603552338712572</v>
       </c>
       <c r="M20" t="n">
-        <v>15.63114584788552</v>
+        <v>15.62278365081429</v>
       </c>
       <c r="N20" t="n">
-        <v>452.1232757734584</v>
+        <v>452.0606563427153</v>
       </c>
       <c r="O20" t="n">
-        <v>21.26319063013494</v>
+        <v>21.26171809479928</v>
       </c>
       <c r="P20" t="n">
-        <v>344.0561205598912</v>
+        <v>343.9198159818872</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28531,28 +28619,28 @@
         <v>0.1793</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4460502602703313</v>
+        <v>-0.4329910195519678</v>
       </c>
       <c r="J21" t="n">
+        <v>300</v>
+      </c>
+      <c r="K21" t="n">
         <v>299</v>
       </c>
-      <c r="K21" t="n">
-        <v>298</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.04624069490769567</v>
+        <v>0.0436989356875932</v>
       </c>
       <c r="M21" t="n">
-        <v>11.22482630101694</v>
+        <v>11.23905010057445</v>
       </c>
       <c r="N21" t="n">
-        <v>222.4672490078395</v>
+        <v>223.131677130996</v>
       </c>
       <c r="O21" t="n">
-        <v>14.91533603402349</v>
+        <v>14.93759274886673</v>
       </c>
       <c r="P21" t="n">
-        <v>339.9746203331882</v>
+        <v>339.8402588792529</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28609,28 +28697,28 @@
         <v>0.1333</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8605062654727469</v>
+        <v>-0.8391714477734887</v>
       </c>
       <c r="J22" t="n">
+        <v>300</v>
+      </c>
+      <c r="K22" t="n">
         <v>299</v>
       </c>
-      <c r="K22" t="n">
-        <v>298</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.06423407857733532</v>
+        <v>0.06128891702969486</v>
       </c>
       <c r="M22" t="n">
-        <v>19.44155344942517</v>
+        <v>19.4419046944335</v>
       </c>
       <c r="N22" t="n">
-        <v>584.7818088411479</v>
+        <v>586.5851551678404</v>
       </c>
       <c r="O22" t="n">
-        <v>24.18226227715571</v>
+        <v>24.21952012670442</v>
       </c>
       <c r="P22" t="n">
-        <v>344.9281252339449</v>
+        <v>344.7086195837056</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28687,28 +28775,28 @@
         <v>0.0785</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.210604512615825</v>
+        <v>-1.185902302166119</v>
       </c>
       <c r="J23" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K23" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1202933999719533</v>
+        <v>0.1157871841943192</v>
       </c>
       <c r="M23" t="n">
-        <v>19.9412845709807</v>
+        <v>19.97751907599674</v>
       </c>
       <c r="N23" t="n">
-        <v>573.4580460875196</v>
+        <v>576.4734440779349</v>
       </c>
       <c r="O23" t="n">
-        <v>23.94698407080774</v>
+        <v>24.00986139230993</v>
       </c>
       <c r="P23" t="n">
-        <v>355.054469768695</v>
+        <v>354.7971554991258</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28746,7 +28834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X300"/>
+  <dimension ref="A1:X301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65129,7 +65217,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>-39.86227145941796,174.81326555761248</t>
+          <t>-39.862269671328995,174.81326635823476</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -65208,6 +65296,128 @@
         </is>
       </c>
       <c r="X300" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:06+00:00</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>-39.86391743441516,174.8182273508965</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>-39.8636628611603,174.8173915396527</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>-39.86334774716967,174.8165828339511</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>-39.86310185764685,174.81574313510268</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>-39.86279678993341,174.81492993246457</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>-39.86253029339214,174.81409946043772</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>-39.862267202063265,174.8132674638559</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>-39.8620454063144,174.8124169768318</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>-39.861783761037806,174.811584332632</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>-39.86157652376061,174.81072732591483</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>-39.861368604418836,174.80987062384946</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>-39.861160769333026,174.80901388329985</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>-39.86095693522434,174.80815535035532</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>-39.86087230454134,174.80724343620673</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>-39.86061397508996,174.80640930463403</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>-39.86042027046755,174.80554623246329</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>-39.86021694346319,174.80468746853307</t>
+        </is>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>-39.85992378725943,174.80386893297666</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>-39.85956668646636,174.8030790353229</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>-39.8593955420156,174.80220585776294</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>-39.859224311386264,174.80133271743657</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>-39.85904047831403,174.8004652200292</t>
+        </is>
+      </c>
+      <c r="X301" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0299/nzd0299.xlsx
+++ b/data/nzd0299/nzd0299.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X301"/>
+  <dimension ref="A1:X302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23882,6 +23882,84 @@
       <c r="X301" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:06:45+00:00</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>354.71</v>
+      </c>
+      <c r="C302" t="n">
+        <v>350.01</v>
+      </c>
+      <c r="D302" t="n">
+        <v>341.76</v>
+      </c>
+      <c r="E302" t="n">
+        <v>340.85</v>
+      </c>
+      <c r="F302" t="n">
+        <v>332.43</v>
+      </c>
+      <c r="G302" t="n">
+        <v>326</v>
+      </c>
+      <c r="H302" t="n">
+        <v>324.06</v>
+      </c>
+      <c r="I302" t="n">
+        <v>333.59</v>
+      </c>
+      <c r="J302" t="n">
+        <v>330.41</v>
+      </c>
+      <c r="K302" t="n">
+        <v>334.98</v>
+      </c>
+      <c r="L302" t="n">
+        <v>338.29</v>
+      </c>
+      <c r="M302" t="n">
+        <v>344.64</v>
+      </c>
+      <c r="N302" t="n">
+        <v>350.95</v>
+      </c>
+      <c r="O302" t="n">
+        <v>361.07</v>
+      </c>
+      <c r="P302" t="n">
+        <v>355.14</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>357.48</v>
+      </c>
+      <c r="R302" t="n">
+        <v>360.14</v>
+      </c>
+      <c r="S302" t="n">
+        <v>350.89</v>
+      </c>
+      <c r="T302" t="n">
+        <v>343.82</v>
+      </c>
+      <c r="U302" t="n">
+        <v>345.27</v>
+      </c>
+      <c r="V302" t="n">
+        <v>348.73</v>
+      </c>
+      <c r="W302" t="n">
+        <v>348.63</v>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23896,7 +23974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B307"/>
+  <dimension ref="A1:B308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26969,6 +27047,16 @@
       </c>
       <c r="B307" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>
@@ -27137,28 +27225,28 @@
         <v>0.0497</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4991914148037344</v>
+        <v>-0.4931743869705774</v>
       </c>
       <c r="J2" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K2" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07207481904875457</v>
+        <v>0.07080926872476911</v>
       </c>
       <c r="M2" t="n">
-        <v>9.200975568221615</v>
+        <v>9.191386208442974</v>
       </c>
       <c r="N2" t="n">
-        <v>175.3940207206007</v>
+        <v>175.10105819047</v>
       </c>
       <c r="O2" t="n">
-        <v>13.24364076531075</v>
+        <v>13.23257564461545</v>
       </c>
       <c r="P2" t="n">
-        <v>358.3825166251711</v>
+        <v>358.3200388365713</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27215,28 +27303,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.311443433205178</v>
+        <v>-0.307691643668997</v>
       </c>
       <c r="J3" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K3" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05688136028324986</v>
+        <v>0.05588958062105598</v>
       </c>
       <c r="M3" t="n">
-        <v>7.568021971891033</v>
+        <v>7.561625583757175</v>
       </c>
       <c r="N3" t="n">
-        <v>86.41710449183155</v>
+        <v>86.23810701087432</v>
       </c>
       <c r="O3" t="n">
-        <v>9.296080060532587</v>
+        <v>9.286447491418574</v>
       </c>
       <c r="P3" t="n">
-        <v>352.3918764603143</v>
+        <v>352.3524071701425</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27293,28 +27381,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.232163620518471</v>
+        <v>-0.2304148227393958</v>
       </c>
       <c r="J4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K4" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01689364414703309</v>
+        <v>0.01675416432319488</v>
       </c>
       <c r="M4" t="n">
-        <v>9.518777693620573</v>
+        <v>9.49518589759527</v>
       </c>
       <c r="N4" t="n">
-        <v>169.8987569691382</v>
+        <v>169.3528717947547</v>
       </c>
       <c r="O4" t="n">
-        <v>13.03452173917932</v>
+        <v>13.01356491491685</v>
       </c>
       <c r="P4" t="n">
-        <v>345.1338644666808</v>
+        <v>345.1155316275908</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27371,28 +27459,28 @@
         <v>0.0751</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4675052558851789</v>
+        <v>-0.4622580391129546</v>
       </c>
       <c r="J5" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K5" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06600528194737765</v>
+        <v>0.06495990213788894</v>
       </c>
       <c r="M5" t="n">
-        <v>8.7604004559853</v>
+        <v>8.757631068902246</v>
       </c>
       <c r="N5" t="n">
-        <v>170.4740254414848</v>
+        <v>170.1250432406452</v>
       </c>
       <c r="O5" t="n">
-        <v>13.05657020206627</v>
+        <v>13.04319911833923</v>
       </c>
       <c r="P5" t="n">
-        <v>344.8772667061452</v>
+        <v>344.8229203820652</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27449,28 +27537,28 @@
         <v>0.0921</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1642352263699711</v>
+        <v>-0.1640337987156474</v>
       </c>
       <c r="J6" t="n">
+        <v>301</v>
+      </c>
+      <c r="K6" t="n">
         <v>300</v>
       </c>
-      <c r="K6" t="n">
-        <v>299</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01281761951122373</v>
+        <v>0.01287298158263139</v>
       </c>
       <c r="M6" t="n">
-        <v>8.367100177998019</v>
+        <v>8.340186818265895</v>
       </c>
       <c r="N6" t="n">
-        <v>113.9018469085391</v>
+        <v>113.5225001346901</v>
       </c>
       <c r="O6" t="n">
-        <v>10.67248082258943</v>
+        <v>10.654693807646</v>
       </c>
       <c r="P6" t="n">
-        <v>336.4147248681368</v>
+        <v>336.4126354172266</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27527,28 +27615,28 @@
         <v>0.0756</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2490937442413236</v>
+        <v>-0.2528275926333121</v>
       </c>
       <c r="J7" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K7" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01816704610174824</v>
+        <v>0.01882091087057136</v>
       </c>
       <c r="M7" t="n">
-        <v>10.49636269551665</v>
+        <v>10.48364921428247</v>
       </c>
       <c r="N7" t="n">
-        <v>180.187196194607</v>
+        <v>179.693536618359</v>
       </c>
       <c r="O7" t="n">
-        <v>13.42338244238787</v>
+        <v>13.40498178358923</v>
       </c>
       <c r="P7" t="n">
-        <v>338.2516959278144</v>
+        <v>338.2909764749293</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27605,28 +27693,28 @@
         <v>0.076</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2791232871367745</v>
+        <v>-0.2834520850114532</v>
       </c>
       <c r="J8" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K8" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02256783235224202</v>
+        <v>0.02339390916653517</v>
       </c>
       <c r="M8" t="n">
-        <v>10.19858058628139</v>
+        <v>10.19026665108708</v>
       </c>
       <c r="N8" t="n">
-        <v>184.4760928718142</v>
+        <v>184.0131776909012</v>
       </c>
       <c r="O8" t="n">
-        <v>13.58219764514617</v>
+        <v>13.56514569368502</v>
       </c>
       <c r="P8" t="n">
-        <v>338.1123627270808</v>
+        <v>338.1573107854918</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27683,28 +27771,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3898703949402894</v>
+        <v>-0.3868942346668608</v>
       </c>
       <c r="J9" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K9" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03948550830739783</v>
+        <v>0.03915151645305792</v>
       </c>
       <c r="M9" t="n">
-        <v>10.81137087224888</v>
+        <v>10.78772230404137</v>
       </c>
       <c r="N9" t="n">
-        <v>201.4299752387081</v>
+        <v>200.8268950002353</v>
       </c>
       <c r="O9" t="n">
-        <v>14.19260283523456</v>
+        <v>14.17134062113515</v>
       </c>
       <c r="P9" t="n">
-        <v>339.1654619371913</v>
+        <v>339.1344263563549</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27761,28 +27849,28 @@
         <v>0.0916</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1765866487245554</v>
+        <v>-0.1768603841713315</v>
       </c>
       <c r="J10" t="n">
+        <v>301</v>
+      </c>
+      <c r="K10" t="n">
         <v>300</v>
       </c>
-      <c r="K10" t="n">
-        <v>299</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.008872380668788815</v>
+        <v>0.008960207813027532</v>
       </c>
       <c r="M10" t="n">
-        <v>10.80551893183642</v>
+        <v>10.77106203916337</v>
       </c>
       <c r="N10" t="n">
-        <v>189.2207540854439</v>
+        <v>188.5906129989894</v>
       </c>
       <c r="O10" t="n">
-        <v>13.7557534902834</v>
+        <v>13.73282975205727</v>
       </c>
       <c r="P10" t="n">
-        <v>335.4506490790168</v>
+        <v>335.4535063828507</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27839,28 +27927,28 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1367780185690439</v>
+        <v>-0.1330733779567727</v>
       </c>
       <c r="J11" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K11" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0060328607831166</v>
+        <v>0.005747524627478739</v>
       </c>
       <c r="M11" t="n">
-        <v>10.51127628281006</v>
+        <v>10.49259755273574</v>
       </c>
       <c r="N11" t="n">
-        <v>168.5126500767631</v>
+        <v>168.0626420343912</v>
       </c>
       <c r="O11" t="n">
-        <v>12.98124223935302</v>
+        <v>12.96389764053971</v>
       </c>
       <c r="P11" t="n">
-        <v>332.7799270405413</v>
+        <v>332.7414599169996</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27917,28 +28005,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01832753733947037</v>
+        <v>-0.01250636991989768</v>
       </c>
       <c r="J12" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K12" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0001026092808606993</v>
+        <v>4.803655751117741e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>11.09555052691373</v>
+        <v>11.08262428807551</v>
       </c>
       <c r="N12" t="n">
-        <v>178.9485510622879</v>
+        <v>178.6252236748243</v>
       </c>
       <c r="O12" t="n">
-        <v>13.37716528500294</v>
+        <v>13.36507477251154</v>
       </c>
       <c r="P12" t="n">
-        <v>329.6905222818387</v>
+        <v>329.6300782091955</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27995,28 +28083,28 @@
         <v>0.0853</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.04211802988837451</v>
+        <v>-0.03282187291195108</v>
       </c>
       <c r="J13" t="n">
+        <v>301</v>
+      </c>
+      <c r="K13" t="n">
         <v>300</v>
       </c>
-      <c r="K13" t="n">
-        <v>299</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.0005083952991394858</v>
+        <v>0.000309800333295307</v>
       </c>
       <c r="M13" t="n">
-        <v>11.12851851617971</v>
+        <v>11.12227854483785</v>
       </c>
       <c r="N13" t="n">
-        <v>189.0347391858188</v>
+        <v>189.0881892220872</v>
       </c>
       <c r="O13" t="n">
-        <v>13.74899047878857</v>
+        <v>13.75093412180014</v>
       </c>
       <c r="P13" t="n">
-        <v>331.3460491879118</v>
+        <v>331.248890296746</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28073,28 +28161,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2625523240601417</v>
+        <v>-0.2499358853492893</v>
       </c>
       <c r="J14" t="n">
+        <v>301</v>
+      </c>
+      <c r="K14" t="n">
         <v>300</v>
       </c>
-      <c r="K14" t="n">
-        <v>299</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.01677397062594976</v>
+        <v>0.01524110422786795</v>
       </c>
       <c r="M14" t="n">
-        <v>11.51616710338232</v>
+        <v>11.52251272179756</v>
       </c>
       <c r="N14" t="n">
-        <v>219.0166461166845</v>
+        <v>219.5456523339577</v>
       </c>
       <c r="O14" t="n">
-        <v>14.79921099642425</v>
+        <v>14.81707300157348</v>
       </c>
       <c r="P14" t="n">
-        <v>338.2819796264869</v>
+        <v>338.1501187727258</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28151,28 +28239,28 @@
         <v>0.0414</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1035351209394346</v>
+        <v>-0.08771443062207672</v>
       </c>
       <c r="J15" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K15" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002456174114798482</v>
+        <v>0.001761456088590352</v>
       </c>
       <c r="M15" t="n">
-        <v>9.632340601580983</v>
+        <v>9.657537988908166</v>
       </c>
       <c r="N15" t="n">
-        <v>234.7117259885568</v>
+        <v>235.8935563476334</v>
       </c>
       <c r="O15" t="n">
-        <v>15.32030436997114</v>
+        <v>15.35882665920914</v>
       </c>
       <c r="P15" t="n">
-        <v>339.3991735572584</v>
+        <v>339.2330625812011</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28229,28 +28317,28 @@
         <v>0.0699</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8212999330525105</v>
+        <v>-0.8000447892351669</v>
       </c>
       <c r="J16" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K16" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06843364063090152</v>
+        <v>0.06514507046457929</v>
       </c>
       <c r="M16" t="n">
-        <v>17.42439173624901</v>
+        <v>17.4292545704237</v>
       </c>
       <c r="N16" t="n">
-        <v>493.5335645277928</v>
+        <v>495.4166808610216</v>
       </c>
       <c r="O16" t="n">
-        <v>22.21561533083864</v>
+        <v>22.25795769743985</v>
       </c>
       <c r="P16" t="n">
-        <v>344.0011399411138</v>
+        <v>343.7769910822557</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28307,28 +28395,28 @@
         <v>0.074</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1392245379716801</v>
+        <v>-0.1209386401384652</v>
       </c>
       <c r="J17" t="n">
+        <v>301</v>
+      </c>
+      <c r="K17" t="n">
         <v>300</v>
       </c>
-      <c r="K17" t="n">
-        <v>299</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.001830479320154232</v>
+        <v>0.00138489424996302</v>
       </c>
       <c r="M17" t="n">
-        <v>18.10161722885368</v>
+        <v>18.08329023775708</v>
       </c>
       <c r="N17" t="n">
-        <v>574.8449502110434</v>
+        <v>575.587848317732</v>
       </c>
       <c r="O17" t="n">
-        <v>23.97592438699796</v>
+        <v>23.99141197007237</v>
       </c>
       <c r="P17" t="n">
-        <v>332.7330512665968</v>
+        <v>332.5423159367747</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28385,28 +28473,28 @@
         <v>0.0771</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4260910309272333</v>
+        <v>-0.4016536332715377</v>
       </c>
       <c r="J18" t="n">
+        <v>301</v>
+      </c>
+      <c r="K18" t="n">
         <v>300</v>
       </c>
-      <c r="K18" t="n">
-        <v>299</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.01293385806198177</v>
+        <v>0.01151550709061699</v>
       </c>
       <c r="M18" t="n">
-        <v>21.69407787395277</v>
+        <v>21.70150159771367</v>
       </c>
       <c r="N18" t="n">
-        <v>753.5335993909932</v>
+        <v>755.7708352890543</v>
       </c>
       <c r="O18" t="n">
-        <v>27.45056646757937</v>
+        <v>27.49128653390114</v>
       </c>
       <c r="P18" t="n">
-        <v>333.347273788084</v>
+        <v>333.0923738020746</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28463,28 +28551,28 @@
         <v>0.1693</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5822608575793635</v>
+        <v>-0.5633569093099595</v>
       </c>
       <c r="J19" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K19" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02571551160779517</v>
+        <v>0.02417843729078917</v>
       </c>
       <c r="M19" t="n">
-        <v>20.98083264931789</v>
+        <v>20.96925174692998</v>
       </c>
       <c r="N19" t="n">
-        <v>692.4881922068421</v>
+        <v>692.9803176103836</v>
       </c>
       <c r="O19" t="n">
-        <v>26.31517038148988</v>
+        <v>26.32451932344414</v>
       </c>
       <c r="P19" t="n">
-        <v>336.9925006716192</v>
+        <v>336.7940167094547</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28541,28 +28629,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.884571135744325</v>
+        <v>-0.8697355888024287</v>
       </c>
       <c r="J20" t="n">
+        <v>301</v>
+      </c>
+      <c r="K20" t="n">
         <v>300</v>
       </c>
-      <c r="K20" t="n">
-        <v>299</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.08603552338712572</v>
+        <v>0.08363930304494138</v>
       </c>
       <c r="M20" t="n">
-        <v>15.62278365081429</v>
+        <v>15.61864707168801</v>
       </c>
       <c r="N20" t="n">
-        <v>452.0606563427153</v>
+        <v>452.3040400164961</v>
       </c>
       <c r="O20" t="n">
-        <v>21.26171809479928</v>
+        <v>21.26744084314086</v>
       </c>
       <c r="P20" t="n">
-        <v>343.9198159818872</v>
+        <v>343.7650703432063</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28619,28 +28707,28 @@
         <v>0.1793</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4329910195519678</v>
+        <v>-0.422199495840516</v>
       </c>
       <c r="J21" t="n">
+        <v>301</v>
+      </c>
+      <c r="K21" t="n">
         <v>300</v>
       </c>
-      <c r="K21" t="n">
-        <v>299</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.0436989356875932</v>
+        <v>0.04174463336547884</v>
       </c>
       <c r="M21" t="n">
-        <v>11.23905010057445</v>
+        <v>11.24287045216489</v>
       </c>
       <c r="N21" t="n">
-        <v>223.131677130996</v>
+        <v>223.3140075264995</v>
       </c>
       <c r="O21" t="n">
-        <v>14.93759274886673</v>
+        <v>14.94369457418411</v>
       </c>
       <c r="P21" t="n">
-        <v>339.8402588792529</v>
+        <v>339.7276953697572</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28697,28 +28785,28 @@
         <v>0.1333</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8391714477734887</v>
+        <v>-0.8224447571514334</v>
       </c>
       <c r="J22" t="n">
+        <v>301</v>
+      </c>
+      <c r="K22" t="n">
         <v>300</v>
       </c>
-      <c r="K22" t="n">
-        <v>299</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.06128891702969486</v>
+        <v>0.05918183805423238</v>
       </c>
       <c r="M22" t="n">
-        <v>19.4419046944335</v>
+        <v>19.42635810862132</v>
       </c>
       <c r="N22" t="n">
-        <v>586.5851551678404</v>
+        <v>586.8547874137231</v>
       </c>
       <c r="O22" t="n">
-        <v>24.21952012670442</v>
+        <v>24.22508591137962</v>
       </c>
       <c r="P22" t="n">
-        <v>344.7086195837056</v>
+        <v>344.5341479290059</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28775,28 +28863,28 @@
         <v>0.0785</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.185902302166119</v>
+        <v>-1.169656257119705</v>
       </c>
       <c r="J23" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K23" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1157871841943192</v>
+        <v>0.1133212844676654</v>
       </c>
       <c r="M23" t="n">
-        <v>19.97751907599674</v>
+        <v>19.97661587717228</v>
       </c>
       <c r="N23" t="n">
-        <v>576.4734440779349</v>
+        <v>576.5902736796345</v>
       </c>
       <c r="O23" t="n">
-        <v>24.00986139230993</v>
+        <v>24.01229421941257</v>
       </c>
       <c r="P23" t="n">
-        <v>354.7971554991258</v>
+        <v>354.6255933164016</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28834,7 +28922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X301"/>
+  <dimension ref="A1:X302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65423,6 +65511,128 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:06:45+00:00</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>-39.86387784058558,174.81824507744793</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>-39.863604449724846,174.8174176914586</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>-39.863300830778265,174.816603839541</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>-39.863059709605885,174.81576200610624</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>-39.862754641966646,174.8149488037187</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-39.86246651809894,174.81412801552452</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>-39.86221662468743,174.8132901100105</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>-39.86206439408008,174.81240847485168</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>-39.86180394082357,174.81157529676423</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>-39.86160947549916,174.8107125709045</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>-39.861404280780484,174.80985464853055</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>-39.86122496963015,174.80898513488003</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>-39.861045316894,174.80811577296754</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>-39.86089810376158,174.80723188305538</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>-39.86061423052732,174.80640919024475</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>-39.86040077211992,174.80555496431776</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>-39.86019003749799,174.80469951792256</t>
+        </is>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>-39.859877893937835,174.80388948584857</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>-39.85958431151486,174.80307114200463</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>-39.859363272061785,174.80222031001617</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>-39.85915934588041,174.8013618130876</t>
+        </is>
+      </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>-39.8589251072895,174.80051689137395</t>
+        </is>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0299/nzd0299.xlsx
+++ b/data/nzd0299/nzd0299.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X302"/>
+  <dimension ref="A1:X305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23958,6 +23958,240 @@
         <v>348.63</v>
       </c>
       <c r="X302" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:28+00:00</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>356.85</v>
+      </c>
+      <c r="C303" t="n">
+        <v>352.53</v>
+      </c>
+      <c r="D303" t="n">
+        <v>342.47</v>
+      </c>
+      <c r="E303" t="n">
+        <v>341.04</v>
+      </c>
+      <c r="F303" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="G303" t="n">
+        <v>326.97</v>
+      </c>
+      <c r="H303" t="n">
+        <v>327.48</v>
+      </c>
+      <c r="I303" t="n">
+        <v>335.27</v>
+      </c>
+      <c r="J303" t="n">
+        <v>333.03</v>
+      </c>
+      <c r="K303" t="n">
+        <v>333.67</v>
+      </c>
+      <c r="L303" t="n">
+        <v>339.83</v>
+      </c>
+      <c r="M303" t="n">
+        <v>346.24</v>
+      </c>
+      <c r="N303" t="n">
+        <v>352.6</v>
+      </c>
+      <c r="O303" t="n">
+        <v>362.35</v>
+      </c>
+      <c r="P303" t="n">
+        <v>356.86</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>358.52</v>
+      </c>
+      <c r="R303" t="n">
+        <v>359.14</v>
+      </c>
+      <c r="S303" t="n">
+        <v>347.35</v>
+      </c>
+      <c r="T303" t="n">
+        <v>339.37</v>
+      </c>
+      <c r="U303" t="n">
+        <v>341.39</v>
+      </c>
+      <c r="V303" t="n">
+        <v>340.83</v>
+      </c>
+      <c r="W303" t="n">
+        <v>337.94</v>
+      </c>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:06:38+00:00</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>356.31</v>
+      </c>
+      <c r="C304" t="n">
+        <v>352.42</v>
+      </c>
+      <c r="D304" t="n">
+        <v>343.03</v>
+      </c>
+      <c r="E304" t="n">
+        <v>342.85</v>
+      </c>
+      <c r="F304" t="n">
+        <v>341.58</v>
+      </c>
+      <c r="G304" t="n">
+        <v>339.23</v>
+      </c>
+      <c r="H304" t="n">
+        <v>341.24</v>
+      </c>
+      <c r="I304" t="n">
+        <v>338.14</v>
+      </c>
+      <c r="J304" t="n">
+        <v>339.04</v>
+      </c>
+      <c r="K304" t="n">
+        <v>338.16</v>
+      </c>
+      <c r="L304" t="n">
+        <v>345.21</v>
+      </c>
+      <c r="M304" t="n">
+        <v>350.65</v>
+      </c>
+      <c r="N304" t="n">
+        <v>354.59</v>
+      </c>
+      <c r="O304" t="n">
+        <v>362.35</v>
+      </c>
+      <c r="P304" t="n">
+        <v>360.1</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>358.1</v>
+      </c>
+      <c r="R304" t="n">
+        <v>355.29</v>
+      </c>
+      <c r="S304" t="n">
+        <v>347.23</v>
+      </c>
+      <c r="T304" t="n">
+        <v>342.95</v>
+      </c>
+      <c r="U304" t="n">
+        <v>340.21</v>
+      </c>
+      <c r="V304" t="n">
+        <v>339.85</v>
+      </c>
+      <c r="W304" t="n">
+        <v>340.73</v>
+      </c>
+      <c r="X304" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35+00:00</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>360.97</v>
+      </c>
+      <c r="C305" t="n">
+        <v>356.65</v>
+      </c>
+      <c r="D305" t="n">
+        <v>350.11</v>
+      </c>
+      <c r="E305" t="n">
+        <v>349.03</v>
+      </c>
+      <c r="F305" t="n">
+        <v>347.23</v>
+      </c>
+      <c r="G305" t="n">
+        <v>342.88</v>
+      </c>
+      <c r="H305" t="n">
+        <v>343.76</v>
+      </c>
+      <c r="I305" t="n">
+        <v>341.81</v>
+      </c>
+      <c r="J305" t="n">
+        <v>342.92</v>
+      </c>
+      <c r="K305" t="n">
+        <v>342.04</v>
+      </c>
+      <c r="L305" t="n">
+        <v>348.08</v>
+      </c>
+      <c r="M305" t="n">
+        <v>355.12</v>
+      </c>
+      <c r="N305" t="n">
+        <v>356.98</v>
+      </c>
+      <c r="O305" t="n">
+        <v>361.97</v>
+      </c>
+      <c r="P305" t="n">
+        <v>363.53</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>362.04</v>
+      </c>
+      <c r="R305" t="n">
+        <v>359.77</v>
+      </c>
+      <c r="S305" t="n">
+        <v>347.23</v>
+      </c>
+      <c r="T305" t="n">
+        <v>342.95</v>
+      </c>
+      <c r="U305" t="n">
+        <v>340.21</v>
+      </c>
+      <c r="V305" t="n">
+        <v>339.85</v>
+      </c>
+      <c r="W305" t="n">
+        <v>340.73</v>
+      </c>
+      <c r="X305" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23974,7 +24208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B308"/>
+  <dimension ref="A1:B311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27057,6 +27291,36 @@
       </c>
       <c r="B308" t="n">
         <v>0.33</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -27225,28 +27489,28 @@
         <v>0.0497</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4931743869705774</v>
+        <v>-0.4694548131337316</v>
       </c>
       <c r="J2" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K2" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07080926872476911</v>
+        <v>0.06526557323932847</v>
       </c>
       <c r="M2" t="n">
-        <v>9.191386208442974</v>
+        <v>9.183784523718902</v>
       </c>
       <c r="N2" t="n">
-        <v>175.10105819047</v>
+        <v>174.9474933377146</v>
       </c>
       <c r="O2" t="n">
-        <v>13.23257564461545</v>
+        <v>13.22677184114531</v>
       </c>
       <c r="P2" t="n">
-        <v>358.3200388365713</v>
+        <v>358.0731074676383</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27303,28 +27567,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.307691643668997</v>
+        <v>-0.2894520955870666</v>
       </c>
       <c r="J3" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K3" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05588958062105598</v>
+        <v>0.0502322482314288</v>
       </c>
       <c r="M3" t="n">
-        <v>7.561625583757175</v>
+        <v>7.578209623911503</v>
       </c>
       <c r="N3" t="n">
-        <v>86.23810701087432</v>
+        <v>86.30440611615374</v>
       </c>
       <c r="O3" t="n">
-        <v>9.286447491418574</v>
+        <v>9.290016475558788</v>
       </c>
       <c r="P3" t="n">
-        <v>352.3524071701425</v>
+        <v>352.1600223404235</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27381,28 +27645,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2304148227393958</v>
+        <v>-0.21880266533062</v>
       </c>
       <c r="J4" t="n">
+        <v>304</v>
+      </c>
+      <c r="K4" t="n">
         <v>301</v>
       </c>
-      <c r="K4" t="n">
-        <v>298</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.01675416432319488</v>
+        <v>0.01539247744806505</v>
       </c>
       <c r="M4" t="n">
-        <v>9.49518589759527</v>
+        <v>9.455091049318611</v>
       </c>
       <c r="N4" t="n">
-        <v>169.3528717947547</v>
+        <v>168.1485434742371</v>
       </c>
       <c r="O4" t="n">
-        <v>13.01356491491685</v>
+        <v>12.9672103196577</v>
       </c>
       <c r="P4" t="n">
-        <v>345.1155316275908</v>
+        <v>344.993420405604</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27459,28 +27723,28 @@
         <v>0.0751</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4622580391129546</v>
+        <v>-0.4405226229631123</v>
       </c>
       <c r="J5" t="n">
+        <v>304</v>
+      </c>
+      <c r="K5" t="n">
         <v>301</v>
       </c>
-      <c r="K5" t="n">
-        <v>298</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.06495990213788894</v>
+        <v>0.06000414897082118</v>
       </c>
       <c r="M5" t="n">
-        <v>8.757631068902246</v>
+        <v>8.779155000159113</v>
       </c>
       <c r="N5" t="n">
-        <v>170.1250432406452</v>
+        <v>169.8473395713948</v>
       </c>
       <c r="O5" t="n">
-        <v>13.04319911833923</v>
+        <v>13.03254923533362</v>
       </c>
       <c r="P5" t="n">
-        <v>344.8229203820652</v>
+        <v>344.5971655615731</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27537,28 +27801,28 @@
         <v>0.0921</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1640337987156474</v>
+        <v>-0.147885444562575</v>
       </c>
       <c r="J6" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K6" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01287298158263139</v>
+        <v>0.01060290474426262</v>
       </c>
       <c r="M6" t="n">
-        <v>8.340186818265895</v>
+        <v>8.336535681401575</v>
       </c>
       <c r="N6" t="n">
-        <v>113.5225001346901</v>
+        <v>113.4320028864723</v>
       </c>
       <c r="O6" t="n">
-        <v>10.654693807646</v>
+        <v>10.65044613556035</v>
       </c>
       <c r="P6" t="n">
-        <v>336.4126354172266</v>
+        <v>336.2445809413344</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27615,28 +27879,28 @@
         <v>0.0756</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2528275926333121</v>
+        <v>-0.2438627155141947</v>
       </c>
       <c r="J7" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K7" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01882091087057136</v>
+        <v>0.01781932027973021</v>
       </c>
       <c r="M7" t="n">
-        <v>10.48364921428247</v>
+        <v>10.4492266285749</v>
       </c>
       <c r="N7" t="n">
-        <v>179.693536618359</v>
+        <v>178.5812395145409</v>
       </c>
       <c r="O7" t="n">
-        <v>13.40498178358923</v>
+        <v>13.36342918245691</v>
       </c>
       <c r="P7" t="n">
-        <v>338.2909764749293</v>
+        <v>338.1962856403297</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27693,28 +27957,28 @@
         <v>0.076</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2834520850114532</v>
+        <v>-0.2707459115250533</v>
       </c>
       <c r="J8" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K8" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02339390916653517</v>
+        <v>0.02170327369751179</v>
       </c>
       <c r="M8" t="n">
-        <v>10.19026665108708</v>
+        <v>10.1681050506502</v>
       </c>
       <c r="N8" t="n">
-        <v>184.0131776909012</v>
+        <v>183.1408468171611</v>
       </c>
       <c r="O8" t="n">
-        <v>13.56514569368502</v>
+        <v>13.53295410533713</v>
       </c>
       <c r="P8" t="n">
-        <v>338.1573107854918</v>
+        <v>338.0249054920776</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27771,28 +28035,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3868942346668608</v>
+        <v>-0.3691442541383009</v>
       </c>
       <c r="J9" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K9" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03915151645305792</v>
+        <v>0.03630605709589274</v>
       </c>
       <c r="M9" t="n">
-        <v>10.78772230404137</v>
+        <v>10.75433052326156</v>
       </c>
       <c r="N9" t="n">
-        <v>200.8268950002353</v>
+        <v>199.7568775199348</v>
       </c>
       <c r="O9" t="n">
-        <v>14.17134062113515</v>
+        <v>14.13353733217324</v>
       </c>
       <c r="P9" t="n">
-        <v>339.1344263563549</v>
+        <v>338.9488147162277</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27849,28 +28113,28 @@
         <v>0.0916</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1768603841713315</v>
+        <v>-0.1626718404166714</v>
       </c>
       <c r="J10" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K10" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008960207813027532</v>
+        <v>0.007715289421656557</v>
       </c>
       <c r="M10" t="n">
-        <v>10.77106203916337</v>
+        <v>10.72906850840901</v>
       </c>
       <c r="N10" t="n">
-        <v>188.5906129989894</v>
+        <v>187.4299424533646</v>
       </c>
       <c r="O10" t="n">
-        <v>13.73282975205727</v>
+        <v>13.69050555872078</v>
       </c>
       <c r="P10" t="n">
-        <v>335.4535063828507</v>
+        <v>335.3049498732295</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27927,28 +28191,28 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1330733779567727</v>
+        <v>-0.116737862654828</v>
       </c>
       <c r="J11" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K11" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005747524627478739</v>
+        <v>0.004496030353439151</v>
       </c>
       <c r="M11" t="n">
-        <v>10.49259755273574</v>
+        <v>10.4594481456724</v>
       </c>
       <c r="N11" t="n">
-        <v>168.0626420343912</v>
+        <v>167.2450556797729</v>
       </c>
       <c r="O11" t="n">
-        <v>12.96389764053971</v>
+        <v>12.9323259965009</v>
       </c>
       <c r="P11" t="n">
-        <v>332.7414599169996</v>
+        <v>332.5713481189088</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28005,28 +28269,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01250636991989768</v>
+        <v>0.01577012439445168</v>
       </c>
       <c r="J12" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K12" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L12" t="n">
-        <v>4.803655751117741e-05</v>
+        <v>7.693586222823345e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>11.08262428807551</v>
+        <v>11.0928747819987</v>
       </c>
       <c r="N12" t="n">
-        <v>178.6252236748243</v>
+        <v>179.1529852853937</v>
       </c>
       <c r="O12" t="n">
-        <v>13.36507477251154</v>
+        <v>13.38480426772815</v>
       </c>
       <c r="P12" t="n">
-        <v>329.6300782091955</v>
+        <v>329.3356834564777</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28083,28 +28347,28 @@
         <v>0.0853</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03282187291195108</v>
+        <v>0.005505083217904895</v>
       </c>
       <c r="J13" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K13" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L13" t="n">
-        <v>0.000309800333295307</v>
+        <v>8.706154196236326e-06</v>
       </c>
       <c r="M13" t="n">
-        <v>11.12227854483785</v>
+        <v>11.14209151262494</v>
       </c>
       <c r="N13" t="n">
-        <v>189.0881892220872</v>
+        <v>191.2966743301786</v>
       </c>
       <c r="O13" t="n">
-        <v>13.75093412180014</v>
+        <v>13.83100409696196</v>
       </c>
       <c r="P13" t="n">
-        <v>331.248890296746</v>
+        <v>330.8472692605892</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28161,28 +28425,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2499358853492893</v>
+        <v>-0.2062470182008523</v>
       </c>
       <c r="J14" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K14" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01524110422786795</v>
+        <v>0.01039535326426166</v>
       </c>
       <c r="M14" t="n">
-        <v>11.52251272179756</v>
+        <v>11.56372454218792</v>
       </c>
       <c r="N14" t="n">
-        <v>219.5456523339577</v>
+        <v>222.5397569041943</v>
       </c>
       <c r="O14" t="n">
-        <v>14.81707300157348</v>
+        <v>14.91776648510742</v>
       </c>
       <c r="P14" t="n">
-        <v>338.1501187727258</v>
+        <v>337.6923701209358</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28239,28 +28503,28 @@
         <v>0.0414</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.08771443062207672</v>
+        <v>-0.03970157424622165</v>
       </c>
       <c r="J15" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K15" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001761456088590352</v>
+        <v>0.0003592744136896586</v>
       </c>
       <c r="M15" t="n">
-        <v>9.657537988908166</v>
+        <v>9.737674896645217</v>
       </c>
       <c r="N15" t="n">
-        <v>235.8935563476334</v>
+        <v>239.7154675474227</v>
       </c>
       <c r="O15" t="n">
-        <v>15.35882665920914</v>
+        <v>15.48274741599251</v>
       </c>
       <c r="P15" t="n">
-        <v>339.2330625812011</v>
+        <v>338.7277526077993</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28317,28 +28581,28 @@
         <v>0.0699</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8000447892351669</v>
+        <v>-0.7288351416668758</v>
       </c>
       <c r="J16" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K16" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06514507046457929</v>
+        <v>0.05430089168767926</v>
       </c>
       <c r="M16" t="n">
-        <v>17.4292545704237</v>
+        <v>17.46933835063819</v>
       </c>
       <c r="N16" t="n">
-        <v>495.4166808610216</v>
+        <v>504.0718587341296</v>
       </c>
       <c r="O16" t="n">
-        <v>22.25795769743985</v>
+        <v>22.45154468481244</v>
       </c>
       <c r="P16" t="n">
-        <v>343.7769910822557</v>
+        <v>343.0241774099646</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28395,28 +28659,28 @@
         <v>0.074</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1209386401384652</v>
+        <v>-0.06406772683014274</v>
       </c>
       <c r="J17" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K17" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00138489424996302</v>
+        <v>0.000390945267188636</v>
       </c>
       <c r="M17" t="n">
-        <v>18.08329023775708</v>
+        <v>18.04211792608462</v>
       </c>
       <c r="N17" t="n">
-        <v>575.587848317732</v>
+        <v>578.6700753229007</v>
       </c>
       <c r="O17" t="n">
-        <v>23.99141197007237</v>
+        <v>24.05556225331058</v>
       </c>
       <c r="P17" t="n">
-        <v>332.5423159367747</v>
+        <v>331.9476498510751</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28473,28 +28737,28 @@
         <v>0.0771</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4016536332715377</v>
+        <v>-0.3347614331095143</v>
       </c>
       <c r="J18" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K18" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01151550709061699</v>
+        <v>0.008059954208716191</v>
       </c>
       <c r="M18" t="n">
-        <v>21.70150159771367</v>
+        <v>21.70157001520713</v>
       </c>
       <c r="N18" t="n">
-        <v>755.7708352890543</v>
+        <v>760.4345811492822</v>
       </c>
       <c r="O18" t="n">
-        <v>27.49128653390114</v>
+        <v>27.5759783353063</v>
       </c>
       <c r="P18" t="n">
-        <v>333.0923738020746</v>
+        <v>332.39295351027</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28551,28 +28815,28 @@
         <v>0.1693</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5633569093099595</v>
+        <v>-0.5154435524504281</v>
       </c>
       <c r="J19" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K19" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02417843729078917</v>
+        <v>0.02054729660214016</v>
       </c>
       <c r="M19" t="n">
-        <v>20.96925174692998</v>
+        <v>20.9071023666405</v>
       </c>
       <c r="N19" t="n">
-        <v>692.9803176103836</v>
+        <v>692.2356356949033</v>
       </c>
       <c r="O19" t="n">
-        <v>26.32451932344414</v>
+        <v>26.31037125726095</v>
       </c>
       <c r="P19" t="n">
-        <v>336.7940167094547</v>
+        <v>336.289750279402</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28629,28 +28893,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8697355888024287</v>
+        <v>-0.8305722143207314</v>
       </c>
       <c r="J20" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K20" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L20" t="n">
-        <v>0.08363930304494138</v>
+        <v>0.07761786165101781</v>
       </c>
       <c r="M20" t="n">
-        <v>15.61864707168801</v>
+        <v>15.58882170529653</v>
       </c>
       <c r="N20" t="n">
-        <v>452.3040400164961</v>
+        <v>452.0038973767878</v>
       </c>
       <c r="O20" t="n">
-        <v>21.26744084314086</v>
+        <v>21.26038328386363</v>
       </c>
       <c r="P20" t="n">
-        <v>343.7650703432063</v>
+        <v>343.3555567589285</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28707,28 +28971,28 @@
         <v>0.1793</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.422199495840516</v>
+        <v>-0.3997014817197403</v>
       </c>
       <c r="J21" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K21" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04174463336547884</v>
+        <v>0.03808578699606113</v>
       </c>
       <c r="M21" t="n">
-        <v>11.24287045216489</v>
+        <v>11.2170493342849</v>
       </c>
       <c r="N21" t="n">
-        <v>223.3140075264995</v>
+        <v>222.4759636150342</v>
       </c>
       <c r="O21" t="n">
-        <v>14.94369457418411</v>
+        <v>14.9156281669608</v>
       </c>
       <c r="P21" t="n">
-        <v>339.7276953697572</v>
+        <v>339.4924737082566</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28785,28 +29049,28 @@
         <v>0.1333</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8224447571514334</v>
+        <v>-0.7900534125508372</v>
       </c>
       <c r="J22" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K22" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05918183805423238</v>
+        <v>0.05566099838604754</v>
       </c>
       <c r="M22" t="n">
-        <v>19.42635810862132</v>
+        <v>19.3291774627829</v>
       </c>
       <c r="N22" t="n">
-        <v>586.8547874137231</v>
+        <v>583.885934831667</v>
       </c>
       <c r="O22" t="n">
-        <v>24.22508591137962</v>
+        <v>24.16373180681467</v>
       </c>
       <c r="P22" t="n">
-        <v>344.5341479290059</v>
+        <v>344.195482620402</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28863,28 +29127,28 @@
         <v>0.0785</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.169656257119705</v>
+        <v>-1.139395762149678</v>
       </c>
       <c r="J23" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K23" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1133212844676654</v>
+        <v>0.1097073946038943</v>
       </c>
       <c r="M23" t="n">
-        <v>19.97661587717228</v>
+        <v>19.89834906947922</v>
       </c>
       <c r="N23" t="n">
-        <v>576.5902736796345</v>
+        <v>573.259638879106</v>
       </c>
       <c r="O23" t="n">
-        <v>24.01229421941257</v>
+        <v>23.94284107784843</v>
       </c>
       <c r="P23" t="n">
-        <v>354.6255933164016</v>
+        <v>354.3052452380429</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28922,7 +29186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X302"/>
+  <dimension ref="A1:X305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65633,6 +65897,372 @@
         </is>
       </c>
     </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:28+00:00</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>-39.863896062262306,174.81823691942455</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>-39.86362590698749,174.81740808467774</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>-39.86330687626628,174.81660113283314</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>-39.863061327409525,174.8157612817651</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>-39.86276230523354,174.81494537258322</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>-39.862474777382936,174.81412431747208</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>-39.86224574499523,174.81327707131936</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>-39.86207869876417,174.8124020697695</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>-39.861826249277975,174.81156530773987</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>-39.861598321293286,174.81071756549608</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>-39.86141739333294,174.8098487769296</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>-39.861238593034514,174.80897903441297</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>-39.86105936600219,174.80810948175525</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>-39.86090900244176,174.80722700251368</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>-39.860628875602465,174.8064026319256</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>-39.860409627264765,174.80555099876</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>-39.8601815229518,174.8047033310186</t>
+        </is>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>-39.85984775249657,174.80390298438093</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>-39.85954642191724,174.80308811072743</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>-39.85933023580127,174.80223510544923</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>-39.85909208145698,174.80139193827998</t>
+        </is>
+      </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>-39.85883408762483,174.80055765632457</t>
+        </is>
+      </c>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:06:38+00:00</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>-39.86389146426916,174.8182389779916</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>-39.863624970360945,174.81740850402144</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>-39.863311644538484,174.81659899796463</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-39.86307673911774,174.815754381461</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>-39.862832551842395,174.8149139204739</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>-39.862579167911484,174.81407757706566</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>-39.862362907389524,174.8132246114488</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>-39.86210313593206,174.81239112774819</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>-39.861877422485236,174.81154239396201</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>-39.861636552120245,174.8107004466223</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>-39.86146320211793,174.8098282644367</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>-39.86127614254131,174.80896221998856</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>-39.861076310077706,174.80810189416866</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>-39.86090900244176,174.80722700251368</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>-39.86065646283611,174.80639027787524</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>-39.86040605114859,174.80555260023536</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>-39.86014874194788,174.80471801142988</t>
+        </is>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>-39.85984673075278,174.8039034419581</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>-39.85957690388585,174.8030744594867</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>-39.859320188690766,174.80223960508854</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>-39.85908373726217,174.80139567532524</t>
+        </is>
+      </c>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>-39.858857842992286,174.80054701702565</t>
+        </is>
+      </c>
+      <c r="X304" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35+00:00</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>-39.863931143245885,174.81822121331177</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>-39.86366098790735,174.81739237834103</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>-39.86337192911959,174.8165720071027</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>-39.86312936030641,174.81573082128432</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>-39.86288066012147,174.8148923805089</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>-39.86261024665437,174.81406366166547</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>-39.862384364453526,174.81321500395384</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>-39.862134384852666,174.81237713567518</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>-39.86191045942881,174.8115276010231</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>-39.861669589002226,174.81068565346047</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>-39.861487639144976,174.80981732188795</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>-39.86131420292341,174.80894517677845</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>-39.86109665999693,174.8080927814343</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>-39.8609057668961,174.80722845142463</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>-39.860685667838304,174.8063771993486</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>-39.86043959852334,174.80553757686488</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>-39.86018688711593,174.8047009287682</t>
+        </is>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>-39.85984673075278,174.8039034419581</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>-39.85957690388585,174.8030744594867</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>-39.859320188690766,174.80223960508854</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>-39.85908373726217,174.80139567532524</t>
+        </is>
+      </c>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>-39.858857842992286,174.80054701702565</t>
+        </is>
+      </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0299/nzd0299.xlsx
+++ b/data/nzd0299/nzd0299.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X305"/>
+  <dimension ref="A1:X309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24192,6 +24192,318 @@
         <v>340.73</v>
       </c>
       <c r="X305" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>364.04</v>
+      </c>
+      <c r="C306" t="n">
+        <v>357.68</v>
+      </c>
+      <c r="D306" t="n">
+        <v>351.29</v>
+      </c>
+      <c r="E306" t="n">
+        <v>351.01</v>
+      </c>
+      <c r="F306" t="n">
+        <v>348.38</v>
+      </c>
+      <c r="G306" t="n">
+        <v>345.21</v>
+      </c>
+      <c r="H306" t="n">
+        <v>344.16</v>
+      </c>
+      <c r="I306" t="n">
+        <v>341.51</v>
+      </c>
+      <c r="J306" t="n">
+        <v>342.48</v>
+      </c>
+      <c r="K306" t="n">
+        <v>342.28</v>
+      </c>
+      <c r="L306" t="n">
+        <v>347.78</v>
+      </c>
+      <c r="M306" t="n">
+        <v>353.69</v>
+      </c>
+      <c r="N306" t="n">
+        <v>355.82</v>
+      </c>
+      <c r="O306" t="n">
+        <v>360.93</v>
+      </c>
+      <c r="P306" t="n">
+        <v>360.91</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>359.75</v>
+      </c>
+      <c r="R306" t="n">
+        <v>357.57</v>
+      </c>
+      <c r="S306" t="n">
+        <v>345.68</v>
+      </c>
+      <c r="T306" t="n">
+        <v>340.61</v>
+      </c>
+      <c r="U306" t="n">
+        <v>339.99</v>
+      </c>
+      <c r="V306" t="n">
+        <v>340.84</v>
+      </c>
+      <c r="W306" t="n">
+        <v>337.79</v>
+      </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:22+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>361.56</v>
+      </c>
+      <c r="C307" t="n">
+        <v>353.85</v>
+      </c>
+      <c r="D307" t="n">
+        <v>349.57</v>
+      </c>
+      <c r="E307" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="F307" t="n">
+        <v>347.58</v>
+      </c>
+      <c r="G307" t="n">
+        <v>343.81</v>
+      </c>
+      <c r="H307" t="n">
+        <v>341.48</v>
+      </c>
+      <c r="I307" t="n">
+        <v>339.25</v>
+      </c>
+      <c r="J307" t="n">
+        <v>340.19</v>
+      </c>
+      <c r="K307" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="L307" t="n">
+        <v>345.69</v>
+      </c>
+      <c r="M307" t="n">
+        <v>350.66</v>
+      </c>
+      <c r="N307" t="n">
+        <v>352.26</v>
+      </c>
+      <c r="O307" t="n">
+        <v>356.1</v>
+      </c>
+      <c r="P307" t="n">
+        <v>356.64</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>355.79</v>
+      </c>
+      <c r="R307" t="n">
+        <v>352.98</v>
+      </c>
+      <c r="S307" t="n">
+        <v>342.28</v>
+      </c>
+      <c r="T307" t="n">
+        <v>338.63</v>
+      </c>
+      <c r="U307" t="n">
+        <v>339.07</v>
+      </c>
+      <c r="V307" t="n">
+        <v>343.18</v>
+      </c>
+      <c r="W307" t="n">
+        <v>341.19</v>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>362.92</v>
+      </c>
+      <c r="C308" t="n">
+        <v>356.29</v>
+      </c>
+      <c r="D308" t="n">
+        <v>352.22</v>
+      </c>
+      <c r="E308" t="n">
+        <v>351.82</v>
+      </c>
+      <c r="F308" t="n">
+        <v>348.2</v>
+      </c>
+      <c r="G308" t="n">
+        <v>344.38</v>
+      </c>
+      <c r="H308" t="n">
+        <v>342.79</v>
+      </c>
+      <c r="I308" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="J308" t="n">
+        <v>340.66</v>
+      </c>
+      <c r="K308" t="n">
+        <v>341.27</v>
+      </c>
+      <c r="L308" t="n">
+        <v>344.9</v>
+      </c>
+      <c r="M308" t="n">
+        <v>349.78</v>
+      </c>
+      <c r="N308" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="O308" t="n">
+        <v>356.43</v>
+      </c>
+      <c r="P308" t="n">
+        <v>347.03</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>355.79</v>
+      </c>
+      <c r="R308" t="n">
+        <v>352.98</v>
+      </c>
+      <c r="S308" t="n">
+        <v>331.39</v>
+      </c>
+      <c r="T308" t="n">
+        <v>335.94</v>
+      </c>
+      <c r="U308" t="n">
+        <v>339.28</v>
+      </c>
+      <c r="V308" t="n">
+        <v>336.1</v>
+      </c>
+      <c r="W308" t="n">
+        <v>335.21</v>
+      </c>
+      <c r="X308" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>362.75</v>
+      </c>
+      <c r="C309" t="n">
+        <v>358.16</v>
+      </c>
+      <c r="D309" t="n">
+        <v>354.69</v>
+      </c>
+      <c r="E309" t="n">
+        <v>353.53</v>
+      </c>
+      <c r="F309" t="n">
+        <v>350.97</v>
+      </c>
+      <c r="G309" t="n">
+        <v>347.03</v>
+      </c>
+      <c r="H309" t="n">
+        <v>344.54</v>
+      </c>
+      <c r="I309" t="n">
+        <v>341.39</v>
+      </c>
+      <c r="J309" t="n">
+        <v>343.05</v>
+      </c>
+      <c r="K309" t="n">
+        <v>342.63</v>
+      </c>
+      <c r="L309" t="n">
+        <v>344.8</v>
+      </c>
+      <c r="M309" t="n">
+        <v>351.38</v>
+      </c>
+      <c r="N309" t="n">
+        <v>352.93</v>
+      </c>
+      <c r="O309" t="n">
+        <v>354.46</v>
+      </c>
+      <c r="P309" t="n">
+        <v>333.78</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>352.05</v>
+      </c>
+      <c r="R309" t="n">
+        <v>347.93</v>
+      </c>
+      <c r="S309" t="n">
+        <v>318.69</v>
+      </c>
+      <c r="T309" t="n">
+        <v>333.79</v>
+      </c>
+      <c r="U309" t="n">
+        <v>337.39</v>
+      </c>
+      <c r="V309" t="n">
+        <v>325.67</v>
+      </c>
+      <c r="W309" t="n">
+        <v>325.86</v>
+      </c>
+      <c r="X309" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24208,7 +24520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B311"/>
+  <dimension ref="A1:B315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27321,6 +27633,46 @@
       </c>
       <c r="B311" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -27489,28 +27841,28 @@
         <v>0.0497</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4694548131337316</v>
+        <v>-0.4280204318802369</v>
       </c>
       <c r="J2" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K2" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06526557323932847</v>
+        <v>0.05512487029842317</v>
       </c>
       <c r="M2" t="n">
-        <v>9.183784523718902</v>
+        <v>9.219352968597141</v>
       </c>
       <c r="N2" t="n">
-        <v>174.9474933377146</v>
+        <v>176.3313852676984</v>
       </c>
       <c r="O2" t="n">
-        <v>13.22677184114531</v>
+        <v>13.27898284010106</v>
       </c>
       <c r="P2" t="n">
-        <v>358.0731074676383</v>
+        <v>357.6399768582056</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27567,28 +27919,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2894520955870666</v>
+        <v>-0.260053546374155</v>
       </c>
       <c r="J3" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K3" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0502322482314288</v>
+        <v>0.04114018986639745</v>
       </c>
       <c r="M3" t="n">
-        <v>7.578209623911503</v>
+        <v>7.626303339054409</v>
       </c>
       <c r="N3" t="n">
-        <v>86.30440611615374</v>
+        <v>87.00586236272885</v>
       </c>
       <c r="O3" t="n">
-        <v>9.290016475558788</v>
+        <v>9.327693303423352</v>
       </c>
       <c r="P3" t="n">
-        <v>352.1600223404235</v>
+        <v>351.8486703406394</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27645,28 +27997,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.21880266533062</v>
+        <v>-0.1876956911100435</v>
       </c>
       <c r="J4" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K4" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01539247744806505</v>
+        <v>0.01152765434254599</v>
       </c>
       <c r="M4" t="n">
-        <v>9.455091049318611</v>
+        <v>9.477054285933045</v>
       </c>
       <c r="N4" t="n">
-        <v>168.1485434742371</v>
+        <v>168.0225168442134</v>
       </c>
       <c r="O4" t="n">
-        <v>12.9672103196577</v>
+        <v>12.96234997383628</v>
       </c>
       <c r="P4" t="n">
-        <v>344.993420405604</v>
+        <v>344.6650755619852</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27723,28 +28075,28 @@
         <v>0.0751</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4405226229631123</v>
+        <v>-0.3954315939777878</v>
       </c>
       <c r="J5" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K5" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06000414897082118</v>
+        <v>0.04892559480820546</v>
       </c>
       <c r="M5" t="n">
-        <v>8.779155000159113</v>
+        <v>8.901421245549873</v>
       </c>
       <c r="N5" t="n">
-        <v>169.8473395713948</v>
+        <v>172.0092826056543</v>
       </c>
       <c r="O5" t="n">
-        <v>13.03254923533362</v>
+        <v>13.11523093985212</v>
       </c>
       <c r="P5" t="n">
-        <v>344.5971655615731</v>
+        <v>344.126911700549</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27801,28 +28153,28 @@
         <v>0.0921</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.147885444562575</v>
+        <v>-0.108062435847052</v>
       </c>
       <c r="J6" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K6" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01060290474426262</v>
+        <v>0.005667635713990649</v>
       </c>
       <c r="M6" t="n">
-        <v>8.336535681401575</v>
+        <v>8.433067228261882</v>
       </c>
       <c r="N6" t="n">
-        <v>113.4320028864723</v>
+        <v>115.3565877011726</v>
       </c>
       <c r="O6" t="n">
-        <v>10.65044613556035</v>
+        <v>10.74041841369193</v>
       </c>
       <c r="P6" t="n">
-        <v>336.2445809413344</v>
+        <v>335.8286550554856</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27879,28 +28231,28 @@
         <v>0.0756</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2438627155141947</v>
+        <v>-0.2110744010776005</v>
       </c>
       <c r="J7" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K7" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01781932027973021</v>
+        <v>0.01359044519793595</v>
       </c>
       <c r="M7" t="n">
-        <v>10.4492266285749</v>
+        <v>10.45584793832178</v>
       </c>
       <c r="N7" t="n">
-        <v>178.5812395145409</v>
+        <v>178.4961480085307</v>
       </c>
       <c r="O7" t="n">
-        <v>13.36342918245691</v>
+        <v>13.360245057952</v>
       </c>
       <c r="P7" t="n">
-        <v>338.1962856403297</v>
+        <v>337.849027868057</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27957,28 +28309,28 @@
         <v>0.076</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2707459115250533</v>
+        <v>-0.2408273724927791</v>
       </c>
       <c r="J8" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K8" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02170327369751179</v>
+        <v>0.0175152183836883</v>
       </c>
       <c r="M8" t="n">
-        <v>10.1681050506502</v>
+        <v>10.16744451811506</v>
       </c>
       <c r="N8" t="n">
-        <v>183.1408468171611</v>
+        <v>182.6819970133463</v>
       </c>
       <c r="O8" t="n">
-        <v>13.53295410533713</v>
+        <v>13.51599041925327</v>
       </c>
       <c r="P8" t="n">
-        <v>338.0249054920776</v>
+        <v>337.7121403059968</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28035,28 +28387,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3691442541383009</v>
+        <v>-0.3417945665988225</v>
       </c>
       <c r="J9" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K9" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03630605709589274</v>
+        <v>0.03183940979481847</v>
       </c>
       <c r="M9" t="n">
-        <v>10.75433052326156</v>
+        <v>10.7266425251021</v>
       </c>
       <c r="N9" t="n">
-        <v>199.7568775199348</v>
+        <v>198.7407408932945</v>
       </c>
       <c r="O9" t="n">
-        <v>14.13353733217324</v>
+        <v>14.09754378937319</v>
       </c>
       <c r="P9" t="n">
-        <v>338.9488147162277</v>
+        <v>338.6616807098924</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28113,28 +28465,28 @@
         <v>0.0916</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1626718404166714</v>
+        <v>-0.1368992312669441</v>
       </c>
       <c r="J10" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K10" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007715289421656557</v>
+        <v>0.005578308319979963</v>
       </c>
       <c r="M10" t="n">
-        <v>10.72906850840901</v>
+        <v>10.7041642353466</v>
       </c>
       <c r="N10" t="n">
-        <v>187.4299424533646</v>
+        <v>186.4055259711938</v>
       </c>
       <c r="O10" t="n">
-        <v>13.69050555872078</v>
+        <v>13.6530409056442</v>
       </c>
       <c r="P10" t="n">
-        <v>335.3049498732295</v>
+        <v>335.0341131796671</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28191,28 +28543,28 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.116737862654828</v>
+        <v>-0.0870438714728886</v>
       </c>
       <c r="J11" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K11" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004496030353439151</v>
+        <v>0.002541863003070799</v>
       </c>
       <c r="M11" t="n">
-        <v>10.4594481456724</v>
+        <v>10.45061010308587</v>
       </c>
       <c r="N11" t="n">
-        <v>167.2450556797729</v>
+        <v>166.9524189376869</v>
       </c>
       <c r="O11" t="n">
-        <v>12.9323259965009</v>
+        <v>12.92100688559862</v>
       </c>
       <c r="P11" t="n">
-        <v>332.5713481189088</v>
+        <v>332.2609336121707</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28269,28 +28621,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01577012439445168</v>
+        <v>0.05466560233026846</v>
       </c>
       <c r="J12" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K12" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="L12" t="n">
-        <v>7.693586222823345e-05</v>
+        <v>0.0009310721778641451</v>
       </c>
       <c r="M12" t="n">
-        <v>11.0928747819987</v>
+        <v>11.11172916032457</v>
       </c>
       <c r="N12" t="n">
-        <v>179.1529852853937</v>
+        <v>180.0587199989089</v>
       </c>
       <c r="O12" t="n">
-        <v>13.38480426772815</v>
+        <v>13.41859605170783</v>
       </c>
       <c r="P12" t="n">
-        <v>329.3356834564777</v>
+        <v>328.9291185317003</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28347,28 +28699,28 @@
         <v>0.0853</v>
       </c>
       <c r="I13" t="n">
-        <v>0.005505083217904895</v>
+        <v>0.05529769780821784</v>
       </c>
       <c r="J13" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K13" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L13" t="n">
-        <v>8.706154196236326e-06</v>
+        <v>0.0008766594184909104</v>
       </c>
       <c r="M13" t="n">
-        <v>11.14209151262494</v>
+        <v>11.17887005836636</v>
       </c>
       <c r="N13" t="n">
-        <v>191.2966743301786</v>
+        <v>194.0372931459019</v>
       </c>
       <c r="O13" t="n">
-        <v>13.83100409696196</v>
+        <v>13.92972695877065</v>
       </c>
       <c r="P13" t="n">
-        <v>330.8472692605892</v>
+        <v>330.3233961447684</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28425,28 +28777,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2062470182008523</v>
+        <v>-0.1551460387750003</v>
       </c>
       <c r="J14" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K14" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01039535326426166</v>
+        <v>0.005917040787349226</v>
       </c>
       <c r="M14" t="n">
-        <v>11.56372454218792</v>
+        <v>11.60132312136458</v>
       </c>
       <c r="N14" t="n">
-        <v>222.5397569041943</v>
+        <v>225.1553928283176</v>
       </c>
       <c r="O14" t="n">
-        <v>14.91776648510742</v>
+        <v>15.00517886692183</v>
       </c>
       <c r="P14" t="n">
-        <v>337.6923701209358</v>
+        <v>337.1547353166629</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28503,28 +28855,28 @@
         <v>0.0414</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.03970157424622165</v>
+        <v>0.007654063967720426</v>
       </c>
       <c r="J15" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K15" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0003592744136896586</v>
+        <v>1.344266180558495e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>9.737674896645217</v>
+        <v>9.811899101395122</v>
       </c>
       <c r="N15" t="n">
-        <v>239.7154675474227</v>
+        <v>241.3366121603548</v>
       </c>
       <c r="O15" t="n">
-        <v>15.48274741599251</v>
+        <v>15.53501246090118</v>
       </c>
       <c r="P15" t="n">
-        <v>338.7277526077993</v>
+        <v>338.2272748429098</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28581,28 +28933,28 @@
         <v>0.0699</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7288351416668758</v>
+        <v>-0.6654772242853961</v>
       </c>
       <c r="J16" t="n">
+        <v>308</v>
+      </c>
+      <c r="K16" t="n">
         <v>304</v>
       </c>
-      <c r="K16" t="n">
-        <v>300</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.05430089168767926</v>
+        <v>0.04597416496316376</v>
       </c>
       <c r="M16" t="n">
-        <v>17.46933835063819</v>
+        <v>17.42638554930702</v>
       </c>
       <c r="N16" t="n">
-        <v>504.0718587341296</v>
+        <v>507.2377503429818</v>
       </c>
       <c r="O16" t="n">
-        <v>22.45154468481244</v>
+        <v>22.52193931132445</v>
       </c>
       <c r="P16" t="n">
-        <v>343.0241774099646</v>
+        <v>342.3518553917978</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28659,28 +29011,28 @@
         <v>0.074</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.06406772683014274</v>
+        <v>-0.001754158363839941</v>
       </c>
       <c r="J17" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K17" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L17" t="n">
-        <v>0.000390945267188636</v>
+        <v>2.966399507142725e-07</v>
       </c>
       <c r="M17" t="n">
-        <v>18.04211792608462</v>
+        <v>17.97075187581768</v>
       </c>
       <c r="N17" t="n">
-        <v>578.6700753229007</v>
+        <v>579.4246403574509</v>
       </c>
       <c r="O17" t="n">
-        <v>24.05556225331058</v>
+        <v>24.07124093929208</v>
       </c>
       <c r="P17" t="n">
-        <v>331.9476498510751</v>
+        <v>331.2933739664353</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28737,28 +29089,28 @@
         <v>0.0771</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3347614331095143</v>
+        <v>-0.2634481049777674</v>
       </c>
       <c r="J18" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K18" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L18" t="n">
-        <v>0.008059954208716191</v>
+        <v>0.005065850202748301</v>
       </c>
       <c r="M18" t="n">
-        <v>21.70157001520713</v>
+        <v>21.64371506939032</v>
       </c>
       <c r="N18" t="n">
-        <v>760.4345811492822</v>
+        <v>761.4147470317446</v>
       </c>
       <c r="O18" t="n">
-        <v>27.5759783353063</v>
+        <v>27.59374470838898</v>
       </c>
       <c r="P18" t="n">
-        <v>332.39295351027</v>
+        <v>331.644190867784</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28815,28 +29167,28 @@
         <v>0.1693</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5154435524504281</v>
+        <v>-0.48659953238623</v>
       </c>
       <c r="J19" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K19" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02054729660214016</v>
+        <v>0.01874522524691491</v>
       </c>
       <c r="M19" t="n">
-        <v>20.9071023666405</v>
+        <v>20.74919188293518</v>
       </c>
       <c r="N19" t="n">
-        <v>692.2356356949033</v>
+        <v>686.3800339896511</v>
       </c>
       <c r="O19" t="n">
-        <v>26.31037125726095</v>
+        <v>26.19885558549554</v>
       </c>
       <c r="P19" t="n">
-        <v>336.289750279402</v>
+        <v>335.9851880958188</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28893,28 +29245,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8305722143207314</v>
+        <v>-0.7922731664697581</v>
       </c>
       <c r="J20" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K20" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07761786165101781</v>
+        <v>0.07238858940856618</v>
       </c>
       <c r="M20" t="n">
-        <v>15.58882170529653</v>
+        <v>15.50794553736047</v>
       </c>
       <c r="N20" t="n">
-        <v>452.0038973767878</v>
+        <v>449.2985265146339</v>
       </c>
       <c r="O20" t="n">
-        <v>21.26038328386363</v>
+        <v>21.19666309857837</v>
       </c>
       <c r="P20" t="n">
-        <v>343.3555567589285</v>
+        <v>342.9534569614969</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28971,28 +29323,28 @@
         <v>0.1793</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3997014817197403</v>
+        <v>-0.3754664089855718</v>
       </c>
       <c r="J21" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K21" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03808578699606113</v>
+        <v>0.03443171355629726</v>
       </c>
       <c r="M21" t="n">
-        <v>11.2170493342849</v>
+        <v>11.16126476138024</v>
       </c>
       <c r="N21" t="n">
-        <v>222.4759636150342</v>
+        <v>220.828776557175</v>
       </c>
       <c r="O21" t="n">
-        <v>14.9156281669608</v>
+        <v>14.86030876385733</v>
       </c>
       <c r="P21" t="n">
-        <v>339.4924737082566</v>
+        <v>339.238006851947</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29049,28 +29401,28 @@
         <v>0.1333</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7900534125508372</v>
+        <v>-0.758338274971104</v>
       </c>
       <c r="J22" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K22" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05566099838604754</v>
+        <v>0.05256448271957426</v>
       </c>
       <c r="M22" t="n">
-        <v>19.3291774627829</v>
+        <v>19.17002915843396</v>
       </c>
       <c r="N22" t="n">
-        <v>583.885934831667</v>
+        <v>578.9917172695916</v>
       </c>
       <c r="O22" t="n">
-        <v>24.16373180681467</v>
+        <v>24.06224672115203</v>
       </c>
       <c r="P22" t="n">
-        <v>344.195482620402</v>
+        <v>343.8626209944017</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -29127,28 +29479,28 @@
         <v>0.0785</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.139395762149678</v>
+        <v>-1.113053726594623</v>
       </c>
       <c r="J23" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K23" t="n">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1097073946038943</v>
+        <v>0.1073976565287885</v>
       </c>
       <c r="M23" t="n">
-        <v>19.89834906947922</v>
+        <v>19.74065006150096</v>
       </c>
       <c r="N23" t="n">
-        <v>573.259638879106</v>
+        <v>567.5599517106901</v>
       </c>
       <c r="O23" t="n">
-        <v>23.94284107784843</v>
+        <v>23.82351677881941</v>
       </c>
       <c r="P23" t="n">
-        <v>354.3052452380429</v>
+        <v>354.0253427267902</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -29186,7 +29538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X305"/>
+  <dimension ref="A1:X309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66263,6 +66615,494 @@
         </is>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>-39.863957283686254,174.8182095099604</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>-39.863669758137014,174.81738845175443</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>-39.8633819765492,174.81656750862132</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>-39.863146219521255,174.81572327287088</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>-39.862890452071625,174.81488799626467</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-39.862630085960674,174.81405477867764</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>-39.86238777033664,174.81321347895414</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>-39.86213183044504,174.81237827944184</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>-39.86190671297138,174.81152927857357</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>-39.86167163252063,174.81068473841907</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-39.86148508475194,174.8098184657087</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>-39.86130202700724,174.80895062908255</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>-39.86108678304876,174.80809720435207</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>-39.86089691171843,174.80723241686454</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>-39.860663359644334,174.80638718936117</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>-39.860420100176306,174.80554630872408</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>-39.86016815511405,174.80470931757756</t>
+        </is>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>-39.859833533228574,174.80390935232867</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>-39.859556979917706,174.80308338236605</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>-39.85931831550066,174.80224044400418</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>-39.859092166601826,174.80139190014685</t>
+        </is>
+      </c>
+      <c r="W306" t="inlineStr">
+        <is>
+          <t>-39.85883281045451,174.80055822832966</t>
+        </is>
+      </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:22+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>-39.86393616697882,174.81821896413416</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>-39.86363714650571,174.8174030525521</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>-39.86336733114326,174.81657406572938</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-39.863138896832034,174.81572655147514</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-39.86288364028022,174.8148910461738</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-39.86261816534751,174.81406011609582</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>-39.86236495091945,174.8132236964495</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>-39.86211258724064,174.8123868958146</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>-39.86188721436302,174.81153800945836</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>-39.86165903082363,174.81069038117346</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>-39.86146728914691,174.80982643432455</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>-39.861276227687576,174.80896218186058</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>-39.86105647103446,174.80811077812646</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>-39.86085578622814,174.80725083326953</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>-39.860627002395205,174.80640347078054</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>-39.860386382509255,174.80556140834705</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>-39.86012907334472,174.80472681967018</t>
+        </is>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>-39.85980458381968,174.80392231700486</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>-39.85954012117493,174.80309093249082</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>-39.859310482160126,174.80224395219648</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>-39.85911209049508,174.80138297699452</t>
+        </is>
+      </c>
+      <c r="W307" t="inlineStr">
+        <is>
+          <t>-39.858861759647766,174.80054526287535</t>
+        </is>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>-39.86394774710878,174.81821377958795</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>-39.86365792258433,174.81739375074</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>-39.86338989528599,174.8165639632071</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>-39.86315311647266,174.81572018488254</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>-39.86288891941857,174.81488868249426</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>-39.862623018740045,174.81405794300434</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>-39.862376105186925,174.81321870207756</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>-39.86211641885218,174.8123851801655</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>-39.86189121626085,174.81153621753043</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>-39.86166303271392,174.81068858921788</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>-39.86146056257836,174.80982944638407</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>-39.86126873481565,174.8089655371213</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>-39.86105212858286,174.8081127226831</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>-39.86085859604433,174.8072495750065</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>-39.86054517729045,174.80644011344597</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>-39.860386382509255,174.80556140834705</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>-39.86012907334472,174.80472681967018</t>
+        </is>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>-39.85971186055687,174.80396384202948</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>-39.85951721712469,174.8031011899779</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>-39.85931227020526,174.8022431514135</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>-39.85905180794429,174.80140997523515</t>
+        </is>
+      </c>
+      <c r="W308" t="inlineStr">
+        <is>
+          <t>-39.85881084312461,174.8005680668145</t>
+        </is>
+      </c>
+      <c r="X308" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>-39.86394629959255,174.81821442765633</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>-39.86367384523429,174.81738662188852</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>-39.86341092676924,174.81655454688814</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-39.86316767670314,174.81571366579405</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-39.86291250524576,174.8148781221798</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-39.86264558275743,174.81404784003135</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>-39.86239100592557,174.81321203020426</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>-39.862130808682004,174.81237873694846</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-39.86191156633669,174.81152710538316</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-39.86167461265165,174.81068340398363</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-39.861459711113994,174.80982982765735</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>-39.86128235821907,174.80895943664677</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>-39.8610621758238,174.8081082235125</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>-39.86084182229294,174.807257086454</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>-39.86043235910034,174.80649063519368</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>-39.860354538044255,174.805575669089</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>-39.860086074881075,174.8047460757631</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>-39.8596037259722,174.80401226868983</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>-39.859498910912926,174.80310938833642</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>-39.85929617779891,174.8022503584587</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>-39.85896300185956,174.80144974798415</t>
+        </is>
+      </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>-39.858731232833414,174.80060372173787</t>
+        </is>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
